--- a/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
+++ b/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57360E0D-98A3-4460-A4B2-11DAB05EA582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6CFEF43-18A2-45E7-8EC2-8DE35FCDAF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{7E2B4120-6872-46F6-A9C6-989E31CF230F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{058FD2C1-76B5-4D20-9B64-46EA82C806FE}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2141,7 +2141,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B30A94C-BEAD-442E-BBB1-F257A4A03F0B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43B2DD21-EE8F-494F-878F-27E43E38AE4F}">
   <dimension ref="B9:T125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2220,7 +2220,7 @@
         <v>14</v>
       </c>
       <c r="E11">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -2276,7 +2276,7 @@
         <v>14</v>
       </c>
       <c r="E12">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -2332,7 +2332,7 @@
         <v>17</v>
       </c>
       <c r="E13">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F13">
         <v>1365</v>
@@ -2388,7 +2388,7 @@
         <v>17</v>
       </c>
       <c r="E14">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F14">
         <v>1365</v>
@@ -2444,7 +2444,7 @@
         <v>20</v>
       </c>
       <c r="E15">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -2500,7 +2500,7 @@
         <v>20</v>
       </c>
       <c r="E16">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -2556,7 +2556,7 @@
         <v>20</v>
       </c>
       <c r="E17">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F17">
         <v>1365</v>
@@ -2612,7 +2612,7 @@
         <v>24</v>
       </c>
       <c r="E18">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F18">
         <v>1365</v>
@@ -2668,7 +2668,7 @@
         <v>24</v>
       </c>
       <c r="E19">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F19">
         <v>1365</v>
@@ -2724,7 +2724,7 @@
         <v>24</v>
       </c>
       <c r="E20">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F20">
         <v>1365</v>
@@ -2780,7 +2780,7 @@
         <v>28</v>
       </c>
       <c r="E21">
-        <v>0.42918750000000006</v>
+        <v>0.38626874999999999</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -2836,7 +2836,7 @@
         <v>28</v>
       </c>
       <c r="E22">
-        <v>0.42918750000000006</v>
+        <v>0.38626874999999999</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2892,7 +2892,7 @@
         <v>28</v>
       </c>
       <c r="E23">
-        <v>0.42918750000000006</v>
+        <v>0.38626874999999999</v>
       </c>
       <c r="F23">
         <v>1365</v>
@@ -2948,7 +2948,7 @@
         <v>32</v>
       </c>
       <c r="E24">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -3004,7 +3004,7 @@
         <v>32</v>
       </c>
       <c r="E25">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -3060,7 +3060,7 @@
         <v>35</v>
       </c>
       <c r="E26">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3116,7 +3116,7 @@
         <v>35</v>
       </c>
       <c r="E27">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3172,7 +3172,7 @@
         <v>35</v>
       </c>
       <c r="E28">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F28">
         <v>1365</v>
@@ -3228,7 +3228,7 @@
         <v>39</v>
       </c>
       <c r="E29">
-        <v>0.47249999999999998</v>
+        <v>0.42524999999999996</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3284,7 +3284,7 @@
         <v>39</v>
       </c>
       <c r="E30">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3340,7 +3340,7 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -3396,7 +3396,7 @@
         <v>43</v>
       </c>
       <c r="E32">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -3452,7 +3452,7 @@
         <v>43</v>
       </c>
       <c r="E33">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -3508,7 +3508,7 @@
         <v>43</v>
       </c>
       <c r="E34">
-        <v>0.45675000000000004</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F34">
         <v>1365</v>
@@ -3564,7 +3564,7 @@
         <v>47</v>
       </c>
       <c r="E35">
-        <v>0.42918750000000006</v>
+        <v>0.38626875000000005</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -3620,7 +3620,7 @@
         <v>47</v>
       </c>
       <c r="E36">
-        <v>0.42918750000000006</v>
+        <v>0.38626875000000005</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -3676,7 +3676,7 @@
         <v>50</v>
       </c>
       <c r="E37">
-        <v>0.44100000000000006</v>
+        <v>0.39690000000000014</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -3732,7 +3732,7 @@
         <v>50</v>
       </c>
       <c r="E38">
-        <v>0.44100000000000006</v>
+        <v>0.39690000000000014</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -3788,7 +3788,7 @@
         <v>17</v>
       </c>
       <c r="E39">
-        <v>0.47249999999999998</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -3844,7 +3844,7 @@
         <v>54</v>
       </c>
       <c r="E40">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3900,7 +3900,7 @@
         <v>56</v>
       </c>
       <c r="E41">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3956,7 +3956,7 @@
         <v>56</v>
       </c>
       <c r="E42">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F42">
         <v>1365</v>
@@ -4012,7 +4012,7 @@
         <v>56</v>
       </c>
       <c r="E43">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F43">
         <v>1365</v>
@@ -4068,7 +4068,7 @@
         <v>56</v>
       </c>
       <c r="E44">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F44">
         <v>1365</v>
@@ -4124,7 +4124,7 @@
         <v>56</v>
       </c>
       <c r="E45">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4180,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="E46">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4236,7 +4236,7 @@
         <v>63</v>
       </c>
       <c r="E47">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4292,7 +4292,7 @@
         <v>63</v>
       </c>
       <c r="E48">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -4348,7 +4348,7 @@
         <v>66</v>
       </c>
       <c r="E49">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F49">
         <v>1365</v>
@@ -4404,7 +4404,7 @@
         <v>66</v>
       </c>
       <c r="E50">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F50">
         <v>1365</v>
@@ -4460,7 +4460,7 @@
         <v>66</v>
       </c>
       <c r="E51">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F51">
         <v>1365</v>
@@ -4516,7 +4516,7 @@
         <v>70</v>
       </c>
       <c r="E52">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -4572,7 +4572,7 @@
         <v>70</v>
       </c>
       <c r="E53">
-        <v>0.20868750000000003</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -4628,7 +4628,7 @@
         <v>70</v>
       </c>
       <c r="E54">
-        <v>0.20868750000000003</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -4684,7 +4684,7 @@
         <v>70</v>
       </c>
       <c r="E55">
-        <v>0.20868750000000003</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F55">
         <v>1365</v>
@@ -4740,7 +4740,7 @@
         <v>75</v>
       </c>
       <c r="E56">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -4796,7 +4796,7 @@
         <v>75</v>
       </c>
       <c r="E57">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -4852,7 +4852,7 @@
         <v>75</v>
       </c>
       <c r="E58">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F58">
         <v>1365</v>
@@ -4908,7 +4908,7 @@
         <v>79</v>
       </c>
       <c r="E59">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -4964,7 +4964,7 @@
         <v>79</v>
       </c>
       <c r="E60">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -5020,7 +5020,7 @@
         <v>82</v>
       </c>
       <c r="E61">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -5076,7 +5076,7 @@
         <v>82</v>
       </c>
       <c r="E62">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5132,7 +5132,7 @@
         <v>82</v>
       </c>
       <c r="E63">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5188,7 +5188,7 @@
         <v>82</v>
       </c>
       <c r="E64">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F64">
         <v>1365</v>
@@ -5244,7 +5244,7 @@
         <v>87</v>
       </c>
       <c r="E65">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F65">
         <v>1365</v>
@@ -5300,7 +5300,7 @@
         <v>87</v>
       </c>
       <c r="E66">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F66">
         <v>1365</v>
@@ -5356,7 +5356,7 @@
         <v>90</v>
       </c>
       <c r="E67">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F67">
         <v>1365</v>
@@ -5412,7 +5412,7 @@
         <v>90</v>
       </c>
       <c r="E68">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F68">
         <v>1365</v>
@@ -5468,7 +5468,7 @@
         <v>93</v>
       </c>
       <c r="E69">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F69">
         <v>1365</v>
@@ -5524,7 +5524,7 @@
         <v>93</v>
       </c>
       <c r="E70">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F70">
         <v>1365</v>
@@ -5580,7 +5580,7 @@
         <v>93</v>
       </c>
       <c r="E71">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -5636,7 +5636,7 @@
         <v>93</v>
       </c>
       <c r="E72">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -5692,7 +5692,7 @@
         <v>93</v>
       </c>
       <c r="E73">
-        <v>0.20868750000000003</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -5748,7 +5748,7 @@
         <v>99</v>
       </c>
       <c r="E74">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -5804,7 +5804,7 @@
         <v>99</v>
       </c>
       <c r="E75">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -5860,7 +5860,7 @@
         <v>99</v>
       </c>
       <c r="E76">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F76">
         <v>1365</v>
@@ -5916,7 +5916,7 @@
         <v>99</v>
       </c>
       <c r="E77">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F77">
         <v>1365</v>
@@ -5972,7 +5972,7 @@
         <v>104</v>
       </c>
       <c r="E78">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -6028,7 +6028,7 @@
         <v>104</v>
       </c>
       <c r="E79">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6084,7 +6084,7 @@
         <v>104</v>
       </c>
       <c r="E80">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F80">
         <v>1365</v>
@@ -6140,7 +6140,7 @@
         <v>39</v>
       </c>
       <c r="E81">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F81">
         <v>1365</v>
@@ -6196,7 +6196,7 @@
         <v>39</v>
       </c>
       <c r="E82">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F82">
         <v>1365</v>
@@ -6252,7 +6252,7 @@
         <v>110</v>
       </c>
       <c r="E83">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6308,7 +6308,7 @@
         <v>110</v>
       </c>
       <c r="E84">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -6364,7 +6364,7 @@
         <v>110</v>
       </c>
       <c r="E85">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F85">
         <v>1365</v>
@@ -6420,7 +6420,7 @@
         <v>114</v>
       </c>
       <c r="E86">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -6476,7 +6476,7 @@
         <v>114</v>
       </c>
       <c r="E87">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -6532,7 +6532,7 @@
         <v>114</v>
       </c>
       <c r="E88">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F88">
         <v>1365</v>
@@ -6588,7 +6588,7 @@
         <v>114</v>
       </c>
       <c r="E89">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F89">
         <v>1365</v>
@@ -6644,7 +6644,7 @@
         <v>114</v>
       </c>
       <c r="E90">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F90">
         <v>1365</v>
@@ -6700,7 +6700,7 @@
         <v>50</v>
       </c>
       <c r="E91">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -6756,7 +6756,7 @@
         <v>50</v>
       </c>
       <c r="E92">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -6812,7 +6812,7 @@
         <v>122</v>
       </c>
       <c r="E93">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F93">
         <v>1365</v>
@@ -6868,7 +6868,7 @@
         <v>122</v>
       </c>
       <c r="E94">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F94">
         <v>1365</v>
@@ -6924,7 +6924,7 @@
         <v>122</v>
       </c>
       <c r="E95">
-        <v>0.19687499999999999</v>
+        <v>0.1771875</v>
       </c>
       <c r="F95">
         <v>1365</v>
@@ -6980,7 +6980,7 @@
         <v>126</v>
       </c>
       <c r="E96">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -7036,7 +7036,7 @@
         <v>126</v>
       </c>
       <c r="E97">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7092,7 +7092,7 @@
         <v>129</v>
       </c>
       <c r="E98">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F98">
         <v>1365</v>
@@ -7148,7 +7148,7 @@
         <v>129</v>
       </c>
       <c r="E99">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F99">
         <v>1365</v>
@@ -7204,7 +7204,7 @@
         <v>129</v>
       </c>
       <c r="E100">
-        <v>0.22837500000000002</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F100">
         <v>1365</v>
@@ -7260,7 +7260,7 @@
         <v>133</v>
       </c>
       <c r="E101">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7316,7 +7316,7 @@
         <v>135</v>
       </c>
       <c r="E102">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -7372,7 +7372,7 @@
         <v>54</v>
       </c>
       <c r="E103">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -7428,7 +7428,7 @@
         <v>54</v>
       </c>
       <c r="E104">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F104">
         <v>1365</v>
@@ -7484,7 +7484,7 @@
         <v>54</v>
       </c>
       <c r="E105">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F105">
         <v>1365</v>
@@ -7540,7 +7540,7 @@
         <v>133</v>
       </c>
       <c r="E106">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -7596,7 +7596,7 @@
         <v>141</v>
       </c>
       <c r="E107">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -7652,7 +7652,7 @@
         <v>141</v>
       </c>
       <c r="E108">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -7708,7 +7708,7 @@
         <v>54</v>
       </c>
       <c r="E109">
-        <v>0.27168749999999997</v>
+        <v>0.24451875000000001</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -7764,7 +7764,7 @@
         <v>144</v>
       </c>
       <c r="E110">
-        <v>0.25987500000000002</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F110">
         <v>1365</v>
@@ -7820,7 +7820,7 @@
         <v>144</v>
       </c>
       <c r="E111">
-        <v>0.25987500000000002</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F111">
         <v>1365</v>
@@ -7876,7 +7876,7 @@
         <v>144</v>
       </c>
       <c r="E112">
-        <v>0.25987500000000002</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -7932,7 +7932,7 @@
         <v>148</v>
       </c>
       <c r="E113">
-        <v>0.25987500000000002</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -7988,7 +7988,7 @@
         <v>148</v>
       </c>
       <c r="E114">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F114">
         <v>1365</v>
@@ -8044,7 +8044,7 @@
         <v>148</v>
       </c>
       <c r="E115">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F115">
         <v>1365</v>
@@ -8100,7 +8100,7 @@
         <v>148</v>
       </c>
       <c r="E116">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F116">
         <v>1365</v>
@@ -8156,7 +8156,7 @@
         <v>148</v>
       </c>
       <c r="E117">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F117">
         <v>1365</v>
@@ -8212,7 +8212,7 @@
         <v>20</v>
       </c>
       <c r="E118">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F118">
         <v>1365</v>
@@ -8268,7 +8268,7 @@
         <v>20</v>
       </c>
       <c r="E119">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F119">
         <v>1365</v>
@@ -8324,7 +8324,7 @@
         <v>20</v>
       </c>
       <c r="E120">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -8380,7 +8380,7 @@
         <v>20</v>
       </c>
       <c r="E121">
-        <v>0.252</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -8436,7 +8436,7 @@
         <v>158</v>
       </c>
       <c r="E122">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -8492,7 +8492,7 @@
         <v>158</v>
       </c>
       <c r="E123">
-        <v>0.24412500000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -8548,7 +8548,7 @@
         <v>161</v>
       </c>
       <c r="E124">
-        <v>0.28743750000000001</v>
+        <v>0.25869375</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -8604,7 +8604,7 @@
         <v>54</v>
       </c>
       <c r="E125">
-        <v>0.27168749999999997</v>
+        <v>0.24451875000000001</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -8634,7 +8634,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C4803D-BC47-4C6A-95D6-CF57217FD5FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F9490BD-2D5E-485E-A706-49417CA09ED7}">
   <dimension ref="B9:T162"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8719,7 +8719,7 @@
         <v>0.69899999999999995</v>
       </c>
       <c r="G11">
-        <v>0.54</v>
+        <v>0.4860000000000001</v>
       </c>
       <c r="H11">
         <v>850</v>
@@ -8772,7 +8772,7 @@
         <v>0.69899999999999995</v>
       </c>
       <c r="G12">
-        <v>0.54</v>
+        <v>0.4860000000000001</v>
       </c>
       <c r="H12">
         <v>850</v>
@@ -8825,7 +8825,7 @@
         <v>0.5</v>
       </c>
       <c r="G13">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H13">
         <v>850</v>
@@ -8878,7 +8878,7 @@
         <v>0.5</v>
       </c>
       <c r="G14">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H14">
         <v>850</v>
@@ -8931,7 +8931,7 @@
         <v>0.4</v>
       </c>
       <c r="G15">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H15">
         <v>850</v>
@@ -8984,7 +8984,7 @@
         <v>0.4</v>
       </c>
       <c r="G16">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H16">
         <v>850</v>
@@ -9037,7 +9037,7 @@
         <v>0.4</v>
       </c>
       <c r="G17">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H17">
         <v>850</v>
@@ -9090,7 +9090,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="G18">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H18">
         <v>850</v>
@@ -9143,7 +9143,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="G19">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H19">
         <v>850</v>
@@ -9196,7 +9196,7 @@
         <v>0.33800000000000002</v>
       </c>
       <c r="G20">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H20">
         <v>850</v>
@@ -9249,7 +9249,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="G21">
-        <v>0.49050000000000005</v>
+        <v>0.44145000000000001</v>
       </c>
       <c r="H21">
         <v>850</v>
@@ -9302,7 +9302,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="G22">
-        <v>0.49050000000000005</v>
+        <v>0.44145000000000001</v>
       </c>
       <c r="H22">
         <v>850</v>
@@ -9355,7 +9355,7 @@
         <v>0.40899999999999997</v>
       </c>
       <c r="G23">
-        <v>0.49050000000000005</v>
+        <v>0.44145000000000001</v>
       </c>
       <c r="H23">
         <v>850</v>
@@ -9408,7 +9408,7 @@
         <v>0.58199999999999996</v>
       </c>
       <c r="G24">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H24">
         <v>850</v>
@@ -9461,7 +9461,7 @@
         <v>0.58199999999999996</v>
       </c>
       <c r="G25">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H25">
         <v>850</v>
@@ -9514,7 +9514,7 @@
         <v>0.4</v>
       </c>
       <c r="G26">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H26">
         <v>850</v>
@@ -9567,7 +9567,7 @@
         <v>0.4</v>
       </c>
       <c r="G27">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H27">
         <v>850</v>
@@ -9620,7 +9620,7 @@
         <v>0.4</v>
       </c>
       <c r="G28">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H28">
         <v>850</v>
@@ -9673,7 +9673,7 @@
         <v>1.294</v>
       </c>
       <c r="G29">
-        <v>0.54</v>
+        <v>0.48599999999999999</v>
       </c>
       <c r="H29">
         <v>850</v>
@@ -9726,7 +9726,7 @@
         <v>0.5</v>
       </c>
       <c r="G30">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H30">
         <v>850</v>
@@ -9779,7 +9779,7 @@
         <v>0.5</v>
       </c>
       <c r="G31">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H31">
         <v>850</v>
@@ -9832,7 +9832,7 @@
         <v>0.4</v>
       </c>
       <c r="G32">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H32">
         <v>850</v>
@@ -9885,7 +9885,7 @@
         <v>0.4</v>
       </c>
       <c r="G33">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H33">
         <v>850</v>
@@ -9938,7 +9938,7 @@
         <v>0.4</v>
       </c>
       <c r="G34">
-        <v>0.52200000000000002</v>
+        <v>0.46980000000000005</v>
       </c>
       <c r="H34">
         <v>850</v>
@@ -9991,7 +9991,7 @@
         <v>0.44</v>
       </c>
       <c r="G35">
-        <v>0.49050000000000005</v>
+        <v>0.44145000000000006</v>
       </c>
       <c r="H35">
         <v>850</v>
@@ -10044,7 +10044,7 @@
         <v>0.44</v>
       </c>
       <c r="G36">
-        <v>0.49050000000000005</v>
+        <v>0.44145000000000006</v>
       </c>
       <c r="H36">
         <v>850</v>
@@ -10097,7 +10097,7 @@
         <v>0.13</v>
       </c>
       <c r="G37">
-        <v>0.50400000000000011</v>
+        <v>0.45360000000000011</v>
       </c>
       <c r="H37">
         <v>977.5</v>
@@ -10150,7 +10150,7 @@
         <v>0.15</v>
       </c>
       <c r="G38">
-        <v>0.50400000000000011</v>
+        <v>0.45360000000000011</v>
       </c>
       <c r="H38">
         <v>977.5</v>
@@ -10203,7 +10203,7 @@
         <v>0.45</v>
       </c>
       <c r="G39">
-        <v>0.54</v>
+        <v>0.48600000000000004</v>
       </c>
       <c r="H39">
         <v>850</v>
@@ -10256,7 +10256,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G40">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H40">
         <v>781.99999999999989</v>
@@ -10309,7 +10309,7 @@
         <v>0.13880000000000001</v>
       </c>
       <c r="G41">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H41">
         <v>781.99999999999989</v>
@@ -10362,7 +10362,7 @@
         <v>0.13880000000000001</v>
       </c>
       <c r="G42">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H42">
         <v>781.99999999999989</v>
@@ -10415,7 +10415,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G43">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H43">
         <v>781.99999999999989</v>
@@ -10468,7 +10468,7 @@
         <v>0.13200000000000001</v>
       </c>
       <c r="G44">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H44">
         <v>781.99999999999989</v>
@@ -10521,7 +10521,7 @@
         <v>0.126</v>
       </c>
       <c r="G45">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H45">
         <v>781.99999999999989</v>
@@ -10574,7 +10574,7 @@
         <v>0.126</v>
       </c>
       <c r="G46">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H46">
         <v>781.99999999999989</v>
@@ -10627,7 +10627,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="G47">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H47">
         <v>781.99999999999989</v>
@@ -10680,7 +10680,7 @@
         <v>0.22500000000000001</v>
       </c>
       <c r="G48">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H48">
         <v>781.99999999999989</v>
@@ -10733,7 +10733,7 @@
         <v>0.25</v>
       </c>
       <c r="G49">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H49">
         <v>781.99999999999989</v>
@@ -10786,7 +10786,7 @@
         <v>0.25</v>
       </c>
       <c r="G50">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H50">
         <v>781.99999999999989</v>
@@ -10839,7 +10839,7 @@
         <v>0.25</v>
       </c>
       <c r="G51">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H51">
         <v>781.99999999999989</v>
@@ -10892,7 +10892,7 @@
         <v>0.123</v>
       </c>
       <c r="G52">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H52">
         <v>781.99999999999989</v>
@@ -10945,7 +10945,7 @@
         <v>0.123</v>
       </c>
       <c r="G53">
-        <v>0.23850000000000002</v>
+        <v>0.21465000000000001</v>
       </c>
       <c r="H53">
         <v>781.99999999999989</v>
@@ -10998,7 +10998,7 @@
         <v>0.123</v>
       </c>
       <c r="G54">
-        <v>0.23850000000000002</v>
+        <v>0.21465000000000001</v>
       </c>
       <c r="H54">
         <v>781.99999999999989</v>
@@ -11051,7 +11051,7 @@
         <v>0.123</v>
       </c>
       <c r="G55">
-        <v>0.23850000000000002</v>
+        <v>0.21465000000000001</v>
       </c>
       <c r="H55">
         <v>781.99999999999989</v>
@@ -11104,7 +11104,7 @@
         <v>0.22</v>
       </c>
       <c r="G56">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H56">
         <v>781.99999999999989</v>
@@ -11157,7 +11157,7 @@
         <v>0.22</v>
       </c>
       <c r="G57">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H57">
         <v>781.99999999999989</v>
@@ -11210,7 +11210,7 @@
         <v>0.22</v>
       </c>
       <c r="G58">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H58">
         <v>781.99999999999989</v>
@@ -11263,7 +11263,7 @@
         <v>0.1</v>
       </c>
       <c r="G59">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H59">
         <v>781.99999999999989</v>
@@ -11316,7 +11316,7 @@
         <v>0.1</v>
       </c>
       <c r="G60">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H60">
         <v>781.99999999999989</v>
@@ -11369,7 +11369,7 @@
         <v>0.1</v>
       </c>
       <c r="G61">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H61">
         <v>781.99999999999989</v>
@@ -11422,7 +11422,7 @@
         <v>0.1</v>
       </c>
       <c r="G62">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H62">
         <v>781.99999999999989</v>
@@ -11475,7 +11475,7 @@
         <v>0.1</v>
       </c>
       <c r="G63">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H63">
         <v>781.99999999999989</v>
@@ -11528,7 +11528,7 @@
         <v>0.1</v>
       </c>
       <c r="G64">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H64">
         <v>781.99999999999989</v>
@@ -11581,7 +11581,7 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="G65">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H65">
         <v>781.99999999999989</v>
@@ -11634,7 +11634,7 @@
         <v>0.20899999999999999</v>
       </c>
       <c r="G66">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H66">
         <v>781.99999999999989</v>
@@ -11687,7 +11687,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="G67">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H67">
         <v>781.99999999999989</v>
@@ -11740,7 +11740,7 @@
         <v>0.14599999999999999</v>
       </c>
       <c r="G68">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H68">
         <v>781.99999999999989</v>
@@ -11793,7 +11793,7 @@
         <v>0.215</v>
       </c>
       <c r="G69">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H69">
         <v>781.99999999999989</v>
@@ -11846,7 +11846,7 @@
         <v>0.215</v>
       </c>
       <c r="G70">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H70">
         <v>781.99999999999989</v>
@@ -11899,7 +11899,7 @@
         <v>0.1</v>
       </c>
       <c r="G71">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H71">
         <v>781.99999999999989</v>
@@ -11952,7 +11952,7 @@
         <v>0.1</v>
       </c>
       <c r="G72">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H72">
         <v>781.99999999999989</v>
@@ -12005,7 +12005,7 @@
         <v>0.1</v>
       </c>
       <c r="G73">
-        <v>0.23850000000000002</v>
+        <v>0.21465000000000001</v>
       </c>
       <c r="H73">
         <v>781.99999999999989</v>
@@ -12058,7 +12058,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G74">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H74">
         <v>781.99999999999989</v>
@@ -12111,7 +12111,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G75">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H75">
         <v>781.99999999999989</v>
@@ -12164,7 +12164,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G76">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H76">
         <v>781.99999999999989</v>
@@ -12217,7 +12217,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G77">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H77">
         <v>781.99999999999989</v>
@@ -12270,7 +12270,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G78">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H78">
         <v>781.99999999999989</v>
@@ -12323,7 +12323,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G79">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H79">
         <v>781.99999999999989</v>
@@ -12376,7 +12376,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G80">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H80">
         <v>781.99999999999989</v>
@@ -12429,7 +12429,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G81">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H81">
         <v>781.99999999999989</v>
@@ -12482,7 +12482,7 @@
         <v>0.22800000000000001</v>
       </c>
       <c r="G82">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H82">
         <v>781.99999999999989</v>
@@ -12535,7 +12535,7 @@
         <v>0.115</v>
       </c>
       <c r="G83">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H83">
         <v>781.99999999999989</v>
@@ -12588,7 +12588,7 @@
         <v>0.115</v>
       </c>
       <c r="G84">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H84">
         <v>781.99999999999989</v>
@@ -12641,7 +12641,7 @@
         <v>0.115</v>
       </c>
       <c r="G85">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H85">
         <v>781.99999999999989</v>
@@ -12694,7 +12694,7 @@
         <v>0.184</v>
       </c>
       <c r="G86">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H86">
         <v>781.99999999999989</v>
@@ -12747,7 +12747,7 @@
         <v>0.184</v>
       </c>
       <c r="G87">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H87">
         <v>781.99999999999989</v>
@@ -12800,7 +12800,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="G88">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H88">
         <v>781.99999999999989</v>
@@ -12853,7 +12853,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="G89">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H89">
         <v>781.99999999999989</v>
@@ -12906,7 +12906,7 @@
         <v>0.19700000000000001</v>
       </c>
       <c r="G90">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H90">
         <v>781.99999999999989</v>
@@ -12959,7 +12959,7 @@
         <v>0.1</v>
       </c>
       <c r="G91">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H91">
         <v>781.99999999999989</v>
@@ -13012,7 +13012,7 @@
         <v>0.1</v>
       </c>
       <c r="G92">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H92">
         <v>781.99999999999989</v>
@@ -13065,7 +13065,7 @@
         <v>0.1</v>
       </c>
       <c r="G93">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H93">
         <v>781.99999999999989</v>
@@ -13118,7 +13118,7 @@
         <v>0.1</v>
       </c>
       <c r="G94">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H94">
         <v>781.99999999999989</v>
@@ -13171,7 +13171,7 @@
         <v>0.1</v>
       </c>
       <c r="G95">
-        <v>0.22500000000000001</v>
+        <v>0.20250000000000001</v>
       </c>
       <c r="H95">
         <v>781.99999999999989</v>
@@ -13224,7 +13224,7 @@
         <v>0.2445</v>
       </c>
       <c r="G96">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H96">
         <v>781.99999999999989</v>
@@ -13277,7 +13277,7 @@
         <v>0.2445</v>
       </c>
       <c r="G97">
-        <v>0.26100000000000001</v>
+        <v>0.23490000000000003</v>
       </c>
       <c r="H97">
         <v>781.99999999999989</v>
@@ -13330,7 +13330,7 @@
         <v>0.155</v>
       </c>
       <c r="G98">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H98">
         <v>781.99999999999989</v>
@@ -13383,7 +13383,7 @@
         <v>0.155</v>
       </c>
       <c r="G99">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H99">
         <v>781.99999999999989</v>
@@ -13436,7 +13436,7 @@
         <v>0.155</v>
       </c>
       <c r="G100">
-        <v>0.26100000000000001</v>
+        <v>0.2349</v>
       </c>
       <c r="H100">
         <v>781.99999999999989</v>
@@ -13489,7 +13489,7 @@
         <v>0.16</v>
       </c>
       <c r="G101">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H101">
         <v>781.99999999999989</v>
@@ -13542,7 +13542,7 @@
         <v>0.184</v>
       </c>
       <c r="G102">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H102">
         <v>781.99999999999989</v>
@@ -13595,7 +13595,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G103">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H103">
         <v>781.99999999999989</v>
@@ -13648,7 +13648,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G104">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H104">
         <v>781.99999999999989</v>
@@ -13701,7 +13701,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G105">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H105">
         <v>781.99999999999989</v>
@@ -13754,7 +13754,7 @@
         <v>0.16</v>
       </c>
       <c r="G106">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H106">
         <v>781.99999999999989</v>
@@ -13807,7 +13807,7 @@
         <v>0.06</v>
       </c>
       <c r="G107">
-        <v>0.27000000000000007</v>
+        <v>0.24300000000000002</v>
       </c>
       <c r="H107">
         <v>1173</v>
@@ -13860,7 +13860,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="G108">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H108">
         <v>1173</v>
@@ -13913,7 +13913,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G109">
-        <v>0.3105</v>
+        <v>0.27945000000000003</v>
       </c>
       <c r="H109">
         <v>1173</v>
@@ -13966,7 +13966,7 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="G110">
-        <v>0.29700000000000004</v>
+        <v>0.26730000000000004</v>
       </c>
       <c r="H110">
         <v>1173</v>
@@ -14019,7 +14019,7 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="G111">
-        <v>0.29700000000000004</v>
+        <v>0.26730000000000004</v>
       </c>
       <c r="H111">
         <v>1173</v>
@@ -14072,7 +14072,7 @@
         <v>0.19600000000000001</v>
       </c>
       <c r="G112">
-        <v>0.29700000000000004</v>
+        <v>0.26730000000000004</v>
       </c>
       <c r="H112">
         <v>1173</v>
@@ -14125,7 +14125,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G113">
-        <v>0.29700000000000004</v>
+        <v>0.26730000000000004</v>
       </c>
       <c r="H113">
         <v>1173</v>
@@ -14178,7 +14178,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G114">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H114">
         <v>1173</v>
@@ -14231,7 +14231,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G115">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H115">
         <v>1173</v>
@@ -14284,7 +14284,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G116">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H116">
         <v>1173</v>
@@ -14337,7 +14337,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G117">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H117">
         <v>1173</v>
@@ -14390,7 +14390,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G118">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H118">
         <v>1173</v>
@@ -14443,7 +14443,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G119">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H119">
         <v>1173</v>
@@ -14496,7 +14496,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G120">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H120">
         <v>1173</v>
@@ -14549,7 +14549,7 @@
         <v>0.16800000000000001</v>
       </c>
       <c r="G121">
-        <v>0.28800000000000003</v>
+        <v>0.25920000000000004</v>
       </c>
       <c r="H121">
         <v>1173</v>
@@ -14602,7 +14602,7 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="G122">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H122">
         <v>1173</v>
@@ -14655,7 +14655,7 @@
         <v>0.13100000000000001</v>
       </c>
       <c r="G123">
-        <v>0.27900000000000003</v>
+        <v>0.25110000000000005</v>
       </c>
       <c r="H123">
         <v>1173</v>
@@ -14708,7 +14708,7 @@
         <v>0.7</v>
       </c>
       <c r="G124">
-        <v>0.32850000000000001</v>
+        <v>0.29565000000000002</v>
       </c>
       <c r="H124">
         <v>1020</v>
@@ -14761,7 +14761,7 @@
         <v>0.21099999999999999</v>
       </c>
       <c r="G125">
-        <v>0.3105</v>
+        <v>0.27945000000000003</v>
       </c>
       <c r="H125">
         <v>1173</v>

--- a/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
+++ b/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{069F01AF-5F47-4FD8-BA8F-6C804CE77D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0044DE15-94D3-4738-8CA8-00A0064FF9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{95C4074E-4CFC-45DE-B2C5-B11D8D92A09F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1E775D7F-9893-472F-9F96-FE22C7A13E39}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2099,7 +2099,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23833576-130F-4BD0-93D5-A1A5CA016961}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE9EBA7-56AF-4655-A20C-2AC84844EF90}">
   <dimension ref="B9:T125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -8592,7 +8592,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C3373E6-5440-4377-B845-B94EB15E3E85}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13125183-6F1E-43D2-AD52-0031AE5A80D9}">
   <dimension ref="B9:T160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
+++ b/VerveStacks_DZA_grids/vt_vervestacks_DZA_v1.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_DZA_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0044DE15-94D3-4738-8CA8-00A0064FF9EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FADBFC12-380A-4974-981F-B9523393F04D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{1E775D7F-9893-472F-9F96-FE22C7A13E39}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{42AA4B29-8207-413D-B3E3-90CE053E45CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
-    <sheet name="existing_stock" sheetId="1" r:id="rId2"/>
+    <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
+    <sheet name="new_options" sheetId="3" r:id="rId2"/>
+    <sheet name="existing_stock" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2721" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3033" uniqueCount="622">
   <si>
     <t>~fi_t</t>
   </si>
@@ -513,67 +515,73 @@
     <t>ep_hydro_dam_G100001051881</t>
   </si>
   <si>
+    <t>ep_solar_pv_001</t>
+  </si>
+  <si>
+    <t>solar</t>
+  </si>
+  <si>
+    <t>elc_spv_001</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_002</t>
+  </si>
+  <si>
+    <t>elc_spv_002</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_003</t>
+  </si>
+  <si>
+    <t>elc_spv_003</t>
+  </si>
+  <si>
     <t>ep_solar_pv_006</t>
   </si>
   <si>
-    <t>solar</t>
-  </si>
-  <si>
     <t>elc_spv_006</t>
   </si>
   <si>
-    <t>ep_solar_pv_009</t>
-  </si>
-  <si>
-    <t>elc_spv_009</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_012</t>
-  </si>
-  <si>
-    <t>elc_spv_012</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_013</t>
-  </si>
-  <si>
-    <t>elc_spv_013</t>
-  </si>
-  <si>
     <t>ep_solar_pv_017</t>
   </si>
   <si>
     <t>elc_spv_017</t>
   </si>
   <si>
+    <t>ep_solar_pv_018</t>
+  </si>
+  <si>
+    <t>elc_spv_018</t>
+  </si>
+  <si>
     <t>ep_solar_pv_019</t>
   </si>
   <si>
     <t>elc_spv_019</t>
   </si>
   <si>
-    <t>ep_solar_pv_021</t>
-  </si>
-  <si>
-    <t>elc_spv_021</t>
-  </si>
-  <si>
     <t>ep_solar_pv_022</t>
   </si>
   <si>
     <t>elc_spv_022</t>
   </si>
   <si>
-    <t>ep_solar_pv_023</t>
-  </si>
-  <si>
-    <t>elc_spv_023</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_029</t>
-  </si>
-  <si>
-    <t>elc_spv_029</t>
+    <t>ep_solar_pv_025</t>
+  </si>
+  <si>
+    <t>elc_spv_025</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_027</t>
+  </si>
+  <si>
+    <t>elc_spv_027</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_030</t>
+  </si>
+  <si>
+    <t>elc_spv_030</t>
   </si>
   <si>
     <t>ep_solar_pv_032</t>
@@ -582,463 +590,616 @@
     <t>elc_spv_032</t>
   </si>
   <si>
-    <t>ep_solar_pv_037</t>
-  </si>
-  <si>
-    <t>elc_spv_037</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_038</t>
+    <t>ep_solar_pv_034</t>
+  </si>
+  <si>
+    <t>elc_spv_034</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_040</t>
+  </si>
+  <si>
+    <t>elc_spv_040</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_043</t>
+  </si>
+  <si>
+    <t>elc_spv_043</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_049</t>
+  </si>
+  <si>
+    <t>elc_spv_049</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_054</t>
+  </si>
+  <si>
+    <t>elc_spv_054</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_055</t>
+  </si>
+  <si>
+    <t>elc_spv_055</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_057</t>
+  </si>
+  <si>
+    <t>elc_spv_057</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_059</t>
+  </si>
+  <si>
+    <t>elc_spv_059</t>
+  </si>
+  <si>
+    <t>ep_solar_pv_062</t>
+  </si>
+  <si>
+    <t>elc_spv_062</t>
+  </si>
+  <si>
+    <t>ep_solar_thermal_032</t>
+  </si>
+  <si>
+    <t>ep_windon_wind_064</t>
+  </si>
+  <si>
+    <t>windon</t>
+  </si>
+  <si>
+    <t>elc_won_064</t>
+  </si>
+  <si>
+    <t>~fi_process</t>
+  </si>
+  <si>
+    <t>set</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>capacity_unit</t>
+  </si>
+  <si>
+    <t>activity_unit</t>
+  </si>
+  <si>
+    <t>timeslicelevel</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>ele</t>
+  </si>
+  <si>
+    <t>Bellara power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Bellara power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Mostaganem power station_2 -- construction</t>
+  </si>
+  <si>
+    <t>Mostaganem power station_3 -- construction</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Arnet power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Arnet power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Arnet power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Hadjret En Nouss power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Hadjret En Nouss power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Hadjret En Nouss power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Naama power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Naama power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Koudiet Eddraouch power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Koudiet Eddraouch power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Koudiet Eddraouch power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Oumache power station_3-1 -- construction</t>
+  </si>
+  <si>
+    <t>Oumache power station_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Oumache power station_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Terga power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Terga power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Terga power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Skikda Combined-Cycle power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Skikda Combined-Cycle power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt I power plant_CC -- operating</t>
+  </si>
+  <si>
+    <t>Hassi R'Mel ISCC power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Mostaganem power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Kais power station_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_3-2 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_3-1 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Ain Djasser power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Boutlélis power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Boutlélis power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Boufarik 2 power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Boufarik 2 power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Boufarik 2 power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messoud Ouest power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messoud Ouest power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messoud Ouest power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messoud Ouest power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messaoud Nord 3 power plant_1-3 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messaoud Nord 3 power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messaoud Nord 3 power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messaoud Nord 2 power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Messaoud Nord 2 power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Berkine South Gas Station_4 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Berkine South Gas Station_3 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Berkine South Gas Station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Hassi Berkine South Gas Station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Hamma 2 power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>Hamma 2 power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>F'Krina power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>F'Krina power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>M'Sila power station_3-2 -- operating</t>
+  </si>
+  <si>
+    <t>M'Sila power station_3-1 -- operating</t>
+  </si>
+  <si>
+    <t>M'Sila power station_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>M'Sila power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>M'Sila power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Larbaa power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>Larbaa power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Larbaa power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Larbaa power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Labreg power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Labreg power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Labreg power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Oumache power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>Oumache power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Kahrama power station_3 -- operating</t>
+  </si>
+  <si>
+    <t>Kahrama power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Kahrama power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt II power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt II power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt III power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt III power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt III power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt I power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Tilghemt I power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tiaret power plant_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>Tiaret power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>Tiaret power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Berrouaghia power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Berrouaghia power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Relizane power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Relizane power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Relizane power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Tamanrasset power plant_1 -- construction</t>
+  </si>
+  <si>
+    <t>Hassasna-Mers El Hadjadj Power Plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Kais power station_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Kais power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>Kais power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>Aggregated Plant -- construction</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Kais power station_2-3 -- construction</t>
+  </si>
+  <si>
+    <t>Jijel power station_3 -- operating</t>
+  </si>
+  <si>
+    <t>Jijel power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>Jijel power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>Marsat El Hadjadj Steam power plant_5 -- operating</t>
+  </si>
+  <si>
+    <t>Marsat El Hadjadj Steam power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>Marsat El Hadjadj Steam power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>Marsat El Hadjadj Steam power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Marsat El Hadjadj Steam power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_1-3 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>Ras Djinet power plant_1-4 -- operating</t>
+  </si>
+  <si>
+    <t>Skikda Steam Gas power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>Skikda Steam Gas power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>Ogla Power Plant_1 -- construction</t>
+  </si>
+  <si>
+    <t>Kais power station_1-3 -- construction</t>
+  </si>
+  <si>
+    <t>Aggregated Plant -- operating</t>
+  </si>
+  <si>
+    <t>Mansouria hydroelectric plant_ -- operating</t>
+  </si>
+  <si>
+    <t>Darguinah hydroelectric plant_ -- operating</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>START</t>
+  </si>
+  <si>
+    <t>cap_bnd</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_010</t>
+  </si>
+  <si>
+    <t>elc_spv_010</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_015</t>
+  </si>
+  <si>
+    <t>elc_spv_015</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_026</t>
+  </si>
+  <si>
+    <t>elc_spv_026</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_027</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_039</t>
+  </si>
+  <si>
+    <t>elc_spv_039</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_058</t>
+  </si>
+  <si>
+    <t>elc_spv_058</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_062</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_G100000831112</t>
+  </si>
+  <si>
+    <t>en_a_solar_pv_G100000831118</t>
+  </si>
+  <si>
+    <t>en_pc_gas_combined_cycle_G100000400816</t>
+  </si>
+  <si>
+    <t>e_w610844609-400</t>
+  </si>
+  <si>
+    <t>en_pc_gas_combined_cycle_G100000400817</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_017</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_020</t>
+  </si>
+  <si>
+    <t>elc_spv_020</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_027</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_032</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_038</t>
   </si>
   <si>
     <t>elc_spv_038</t>
   </si>
   <si>
-    <t>ep_solar_pv_043</t>
-  </si>
-  <si>
-    <t>elc_spv_043</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_047</t>
-  </si>
-  <si>
-    <t>elc_spv_047</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_048</t>
-  </si>
-  <si>
-    <t>elc_spv_048</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_053</t>
-  </si>
-  <si>
-    <t>elc_spv_053</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_054</t>
-  </si>
-  <si>
-    <t>elc_spv_054</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_059</t>
-  </si>
-  <si>
-    <t>elc_spv_059</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_061</t>
-  </si>
-  <si>
-    <t>elc_spv_061</t>
-  </si>
-  <si>
-    <t>ep_solar_pv_063</t>
-  </si>
-  <si>
-    <t>elc_spv_063</t>
-  </si>
-  <si>
-    <t>ep_solar_thermal_023</t>
-  </si>
-  <si>
-    <t>ep_windon_wind_024</t>
-  </si>
-  <si>
-    <t>windon</t>
-  </si>
-  <si>
-    <t>elc_won_024</t>
-  </si>
-  <si>
-    <t>~fi_process</t>
-  </si>
-  <si>
-    <t>set</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>capacity_unit</t>
-  </si>
-  <si>
-    <t>activity_unit</t>
-  </si>
-  <si>
-    <t>timeslicelevel</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>ele</t>
-  </si>
-  <si>
-    <t>Bellara power station_1</t>
-  </si>
-  <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>Bellara power station_2</t>
-  </si>
-  <si>
-    <t>Mostaganem power station_2</t>
-  </si>
-  <si>
-    <t>Mostaganem power station_3</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_2-1</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_2-2</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_2-3</t>
-  </si>
-  <si>
-    <t>Ain Arnet power plant_3</t>
-  </si>
-  <si>
-    <t>Ain Arnet power plant_2</t>
-  </si>
-  <si>
-    <t>Ain Arnet power plant_1</t>
-  </si>
-  <si>
-    <t>Hadjret En Nouss power plant_3</t>
-  </si>
-  <si>
-    <t>Hadjret En Nouss power plant_2</t>
-  </si>
-  <si>
-    <t>Hadjret En Nouss power plant_1</t>
-  </si>
-  <si>
-    <t>Naama power station_2</t>
-  </si>
-  <si>
-    <t>Naama power station_1</t>
-  </si>
-  <si>
-    <t>Koudiet Eddraouch power plant_3</t>
-  </si>
-  <si>
-    <t>Koudiet Eddraouch power plant_2</t>
-  </si>
-  <si>
-    <t>Koudiet Eddraouch power plant_1</t>
-  </si>
-  <si>
-    <t>Oumache power station_3-1</t>
-  </si>
-  <si>
-    <t>Oumache power station_1-2</t>
-  </si>
-  <si>
-    <t>Oumache power station_1-1</t>
-  </si>
-  <si>
-    <t>Terga power plant_3</t>
-  </si>
-  <si>
-    <t>Terga power plant_2</t>
-  </si>
-  <si>
-    <t>Terga power plant_1</t>
-  </si>
-  <si>
-    <t>Skikda Combined-Cycle power plant_2</t>
-  </si>
-  <si>
-    <t>Skikda Combined-Cycle power plant_1</t>
-  </si>
-  <si>
-    <t>Tilghemt I power plant_CC</t>
-  </si>
-  <si>
-    <t>Hassi R'Mel ISCC power station_1</t>
-  </si>
-  <si>
-    <t>Mostaganem power station_1</t>
-  </si>
-  <si>
-    <t>Kais power station_1-1</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_3-2</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_3-1</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_2-2</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_2-1</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_1-2</t>
-  </si>
-  <si>
-    <t>Ain Djasser power plant_1-1</t>
-  </si>
-  <si>
-    <t>Boutlélis power station_2</t>
-  </si>
-  <si>
-    <t>Boutlélis power station_1</t>
-  </si>
-  <si>
-    <t>Boufarik 2 power plant_3</t>
-  </si>
-  <si>
-    <t>Boufarik 2 power plant_2</t>
-  </si>
-  <si>
-    <t>Boufarik 2 power plant_1</t>
-  </si>
-  <si>
-    <t>Hassi Messoud Ouest power plant_4</t>
-  </si>
-  <si>
-    <t>Hassi Messoud Ouest power plant_3</t>
-  </si>
-  <si>
-    <t>Hassi Messoud Ouest power plant_2</t>
-  </si>
-  <si>
-    <t>Hassi Messoud Ouest power plant_1</t>
-  </si>
-  <si>
-    <t>Hassi Messaoud Nord 3 power plant_1-3</t>
-  </si>
-  <si>
-    <t>Hassi Messaoud Nord 3 power plant_1-2</t>
-  </si>
-  <si>
-    <t>Hassi Messaoud Nord 3 power plant_1-1</t>
-  </si>
-  <si>
-    <t>Hassi Messaoud Nord 2 power plant_1-2</t>
-  </si>
-  <si>
-    <t>Hassi Messaoud Nord 2 power plant_1-1</t>
-  </si>
-  <si>
-    <t>Hassi Berkine South Gas Station_4</t>
-  </si>
-  <si>
-    <t>Hassi Berkine South Gas Station_3</t>
-  </si>
-  <si>
-    <t>Hassi Berkine South Gas Station_2</t>
-  </si>
-  <si>
-    <t>Hassi Berkine South Gas Station_1</t>
-  </si>
-  <si>
-    <t>Hamma 2 power plant_4</t>
-  </si>
-  <si>
-    <t>Hamma 2 power plant_3</t>
-  </si>
-  <si>
-    <t>F'Krina power station_2</t>
-  </si>
-  <si>
-    <t>F'Krina power station_1</t>
-  </si>
-  <si>
-    <t>M'Sila power station_3-2</t>
-  </si>
-  <si>
-    <t>M'Sila power station_3-1</t>
-  </si>
-  <si>
-    <t>M'Sila power station_2-3</t>
-  </si>
-  <si>
-    <t>M'Sila power station_2-2</t>
-  </si>
-  <si>
-    <t>M'Sila power station_2-1</t>
-  </si>
-  <si>
-    <t>Larbaa power plant_4</t>
-  </si>
-  <si>
-    <t>Larbaa power plant_3</t>
-  </si>
-  <si>
-    <t>Larbaa power plant_2</t>
-  </si>
-  <si>
-    <t>Larbaa power plant_1</t>
-  </si>
-  <si>
-    <t>Labreg power plant_3</t>
-  </si>
-  <si>
-    <t>Labreg power plant_2</t>
-  </si>
-  <si>
-    <t>Labreg power plant_1</t>
-  </si>
-  <si>
-    <t>Oumache power station_2-2</t>
-  </si>
-  <si>
-    <t>Oumache power station_2-1</t>
-  </si>
-  <si>
-    <t>Kahrama power station_3</t>
-  </si>
-  <si>
-    <t>Kahrama power station_2</t>
-  </si>
-  <si>
-    <t>Kahrama power station_1</t>
-  </si>
-  <si>
-    <t>Tilghemt II power plant_2</t>
-  </si>
-  <si>
-    <t>Tilghemt II power plant_1</t>
-  </si>
-  <si>
-    <t>Tilghemt III power plant_3</t>
-  </si>
-  <si>
-    <t>Tilghemt III power plant_2</t>
-  </si>
-  <si>
-    <t>Tilghemt III power plant_1</t>
-  </si>
-  <si>
-    <t>Tilghemt I power plant_2</t>
-  </si>
-  <si>
-    <t>Tilghemt I power plant_1</t>
-  </si>
-  <si>
-    <t>Tiaret power plant_2-3</t>
-  </si>
-  <si>
-    <t>Tiaret power plant_2-2</t>
-  </si>
-  <si>
-    <t>Tiaret power plant_2-1</t>
-  </si>
-  <si>
-    <t>Berrouaghia power plant_2</t>
-  </si>
-  <si>
-    <t>Berrouaghia power plant_1</t>
-  </si>
-  <si>
-    <t>Relizane power plant_3</t>
-  </si>
-  <si>
-    <t>Relizane power plant_2</t>
-  </si>
-  <si>
-    <t>Relizane power plant_1</t>
-  </si>
-  <si>
-    <t>Tamanrasset power plant_1</t>
-  </si>
-  <si>
-    <t>Hassasna-Mers El Hadjadj Power Plant_1</t>
-  </si>
-  <si>
-    <t>Kais power station_1-2</t>
-  </si>
-  <si>
-    <t>Kais power station_2-1</t>
-  </si>
-  <si>
-    <t>Kais power station_2-2</t>
-  </si>
-  <si>
-    <t>Aggregated Plant</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Kais power station_2-3</t>
-  </si>
-  <si>
-    <t>Jijel power station_3</t>
-  </si>
-  <si>
-    <t>Jijel power station_2</t>
-  </si>
-  <si>
-    <t>Jijel power station_1</t>
-  </si>
-  <si>
-    <t>Marsat El Hadjadj Steam power plant_5</t>
-  </si>
-  <si>
-    <t>Marsat El Hadjadj Steam power plant_4</t>
-  </si>
-  <si>
-    <t>Marsat El Hadjadj Steam power plant_3</t>
-  </si>
-  <si>
-    <t>Marsat El Hadjadj Steam power plant_2</t>
-  </si>
-  <si>
-    <t>Marsat El Hadjadj Steam power plant_1</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_1-3</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_1-2</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_1-1</t>
-  </si>
-  <si>
-    <t>Ras Djinet power plant_1-4</t>
-  </si>
-  <si>
-    <t>Skikda Steam Gas power plant_2</t>
-  </si>
-  <si>
-    <t>Skikda Steam Gas power plant_1</t>
-  </si>
-  <si>
-    <t>Ogla Power Plant_1</t>
-  </si>
-  <si>
-    <t>Kais power station_1-3</t>
-  </si>
-  <si>
-    <t>Mansouria hydroelectric plant_</t>
-  </si>
-  <si>
-    <t>Darguinah hydroelectric plant_</t>
-  </si>
-  <si>
-    <t>annual</t>
+    <t>en_pc_solar_pv_039</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100000831104</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100000831117</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100000831119</t>
+  </si>
+  <si>
+    <t>elc_spv_007</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018561</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018562</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018607</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018621</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018623</t>
+  </si>
+  <si>
+    <t>en_pc_solar_pv_G100001018624</t>
+  </si>
+  <si>
+    <t>Aggregated Plant -- announced</t>
+  </si>
+  <si>
+    <t>El Oued solar farm_Nakhla Solar PV Plant -- announced</t>
+  </si>
+  <si>
+    <t>M'Ghaier solar farm_-- -- announced</t>
+  </si>
+  <si>
+    <t>Djelfa power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>Djelfa power station_2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>Aggregated Plant -- pre-construction</t>
+  </si>
+  <si>
+    <t>Biskra solar farm_Leghrous Solar PV Plant -- pre-construction</t>
+  </si>
+  <si>
+    <t>Laghouat solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>M'Sila solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Fadel solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Tendla solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Laghouat (Özgün İnşaat) solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Hassi Delaa solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Foulia solar farm_-- -- pre-construction</t>
+  </si>
+  <si>
+    <t>Tamacine solar farm_-- -- pre-construction</t>
   </si>
   <si>
     <t>AF</t>
@@ -1050,6 +1211,12 @@
     <t>prc_refit</t>
   </si>
   <si>
+    <t>en_pc_gas_combined_cycle_G100000400816_ccs-rf</t>
+  </si>
+  <si>
+    <t>en_pc_gas_combined_cycle_G100000400817_ccs-rf</t>
+  </si>
+  <si>
     <t>ep_gas_combined_cycle_G100000400814_ccs-rf</t>
   </si>
   <si>
@@ -1392,343 +1559,352 @@
     <t>ep_gas_steam_turbine_w173677993-400_ccs-rf</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Bellara power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Bellara power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Mostaganem power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Mostaganem power station_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_2-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Arnet power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Arnet power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Arnet power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hadjret En Nouss power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hadjret En Nouss power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hadjret En Nouss power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Naama power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Naama power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Koudiet Eddraouch power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Koudiet Eddraouch power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Koudiet Eddraouch power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Oumache power station_3-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Oumache power station_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Oumache power station_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Terga power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Terga power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Terga power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Skikda Combined-Cycle power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Skikda Combined-Cycle power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt I power plant_CC</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi R'Mel ISCC power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Mostaganem power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_3-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_3-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ain Djasser power plant_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Boutlélis power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Boutlélis power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Boufarik 2 power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Boufarik 2 power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Boufarik 2 power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messaoud Nord 2 power plant_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Messaoud Nord 2 power plant_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Berkine South Gas Station_4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Berkine South Gas Station_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Berkine South Gas Station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassi Berkine South Gas Station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hamma 2 power plant_4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hamma 2 power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- F'Krina power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- F'Krina power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- M'Sila power station_3-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- M'Sila power station_3-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- M'Sila power station_2-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- M'Sila power station_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- M'Sila power station_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Larbaa power plant_4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Larbaa power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Larbaa power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Larbaa power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Labreg power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Labreg power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Labreg power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Oumache power station_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Oumache power station_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kahrama power station_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kahrama power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kahrama power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt II power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt II power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt III power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt III power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt III power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt I power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tilghemt I power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tiaret power plant_2-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tiaret power plant_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tiaret power plant_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Berrouaghia power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Berrouaghia power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Relizane power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Relizane power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Relizane power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Tamanrasset power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Hassasna-Mers El Hadjadj Power Plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_2-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_2-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_2-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Jijel power station_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Jijel power station_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Jijel power station_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_5</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_1-3</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_1-2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_1-1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ras Djinet power plant_1-4</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Skikda Steam Gas power plant_2</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Skikda Steam Gas power plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Ogla Power Plant_1</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Kais power station_1-3</t>
+    <t>ccs retrofit of -- Djelfa power station_1 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Djelfa power station_2 -- pre-construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Bellara power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Bellara power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Mostaganem power station_2 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Mostaganem power station_3 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Arnet power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Arnet power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Arnet power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hadjret En Nouss power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hadjret En Nouss power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hadjret En Nouss power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Naama power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Naama power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Koudiet Eddraouch power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Koudiet Eddraouch power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Koudiet Eddraouch power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Oumache power station_3-1 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Oumache power station_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Oumache power station_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Terga power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Terga power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Terga power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Skikda Combined-Cycle power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Skikda Combined-Cycle power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt I power plant_CC -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi R'Mel ISCC power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Mostaganem power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_3-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_3-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ain Djasser power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Boutlélis power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Boutlélis power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Boufarik 2 power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Boufarik 2 power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Boufarik 2 power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messoud Ouest power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messaoud Nord 3 power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messaoud Nord 2 power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Messaoud Nord 2 power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Berkine South Gas Station_4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Berkine South Gas Station_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Berkine South Gas Station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassi Berkine South Gas Station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hamma 2 power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hamma 2 power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- F'Krina power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- F'Krina power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- M'Sila power station_3-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- M'Sila power station_3-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- M'Sila power station_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- M'Sila power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- M'Sila power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Larbaa power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Larbaa power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Larbaa power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Larbaa power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Labreg power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Labreg power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Labreg power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Oumache power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Oumache power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kahrama power station_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kahrama power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kahrama power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt II power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt II power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt III power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt III power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt III power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt I power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tilghemt I power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tiaret power plant_2-3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tiaret power plant_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tiaret power plant_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Berrouaghia power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Berrouaghia power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Relizane power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Relizane power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Relizane power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Tamanrasset power plant_1 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Hassasna-Mers El Hadjadj Power Plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_2-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_2-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_2-3 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jijel power station_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jijel power station_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Jijel power station_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_5 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Marsat El Hadjadj Steam power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_1-3 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_1-2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_1-1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ras Djinet power plant_1-4 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Skikda Steam Gas power plant_2 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Skikda Steam Gas power plant_1 -- operating</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Ogla Power Plant_1 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Kais power station_1-3 -- construction</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant -- operating</t>
   </si>
 </sst>
 </file>
@@ -2099,8 +2275,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE9EBA7-56AF-4655-A20C-2AC84844EF90}">
-  <dimension ref="B9:T125"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B11A24B-23A9-4EE5-A797-A82E4B683EA8}">
+  <dimension ref="B9:T126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="9" spans="2:20" x14ac:dyDescent="0.45">
@@ -2134,13 +2310,13 @@
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>334</v>
+        <v>387</v>
       </c>
       <c r="J10" t="s">
-        <v>335</v>
+        <v>388</v>
       </c>
       <c r="K10" t="s">
-        <v>336</v>
+        <v>389</v>
       </c>
       <c r="L10" t="s">
         <v>10</v>
@@ -2169,16 +2345,16 @@
     </row>
     <row r="11" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="E11">
-        <v>0.42525000000000007</v>
+        <v>0.47249999999999998</v>
       </c>
       <c r="F11">
         <v>1365</v>
@@ -2193,7 +2369,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J11" t="s">
-        <v>12</v>
+        <v>351</v>
       </c>
       <c r="K11">
         <v>1</v>
@@ -2205,10 +2381,10 @@
         <v>212</v>
       </c>
       <c r="O11" t="s">
-        <v>337</v>
+        <v>390</v>
       </c>
       <c r="P11" t="s">
-        <v>451</v>
+        <v>506</v>
       </c>
       <c r="Q11" t="s">
         <v>214</v>
@@ -2225,16 +2401,16 @@
     </row>
     <row r="12" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>14</v>
+        <v>352</v>
       </c>
       <c r="E12">
-        <v>0.42525000000000007</v>
+        <v>0.47249999999999998</v>
       </c>
       <c r="F12">
         <v>1365</v>
@@ -2249,7 +2425,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J12" t="s">
-        <v>15</v>
+        <v>353</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -2261,10 +2437,10 @@
         <v>212</v>
       </c>
       <c r="O12" t="s">
-        <v>338</v>
+        <v>391</v>
       </c>
       <c r="P12" t="s">
-        <v>452</v>
+        <v>507</v>
       </c>
       <c r="Q12" t="s">
         <v>214</v>
@@ -2281,13 +2457,13 @@
     </row>
     <row r="13" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E13">
         <v>0.42525000000000007</v>
@@ -2305,7 +2481,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -2317,10 +2493,10 @@
         <v>212</v>
       </c>
       <c r="O13" t="s">
-        <v>339</v>
+        <v>392</v>
       </c>
       <c r="P13" t="s">
-        <v>453</v>
+        <v>508</v>
       </c>
       <c r="Q13" t="s">
         <v>214</v>
@@ -2337,13 +2513,13 @@
     </row>
     <row r="14" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E14">
         <v>0.42525000000000007</v>
@@ -2361,7 +2537,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J14" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -2373,10 +2549,10 @@
         <v>212</v>
       </c>
       <c r="O14" t="s">
-        <v>340</v>
+        <v>393</v>
       </c>
       <c r="P14" t="s">
-        <v>454</v>
+        <v>509</v>
       </c>
       <c r="Q14" t="s">
         <v>214</v>
@@ -2393,16 +2569,16 @@
     </row>
     <row r="15" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E15">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F15">
         <v>1365</v>
@@ -2417,7 +2593,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -2429,10 +2605,10 @@
         <v>212</v>
       </c>
       <c r="O15" t="s">
-        <v>341</v>
+        <v>394</v>
       </c>
       <c r="P15" t="s">
-        <v>455</v>
+        <v>510</v>
       </c>
       <c r="Q15" t="s">
         <v>214</v>
@@ -2449,16 +2625,16 @@
     </row>
     <row r="16" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E16">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F16">
         <v>1365</v>
@@ -2473,7 +2649,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J16" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -2485,10 +2661,10 @@
         <v>212</v>
       </c>
       <c r="O16" t="s">
-        <v>342</v>
+        <v>395</v>
       </c>
       <c r="P16" t="s">
-        <v>456</v>
+        <v>511</v>
       </c>
       <c r="Q16" t="s">
         <v>214</v>
@@ -2505,7 +2681,7 @@
     </row>
     <row r="17" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -2529,7 +2705,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J17" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -2541,10 +2717,10 @@
         <v>212</v>
       </c>
       <c r="O17" t="s">
-        <v>343</v>
+        <v>396</v>
       </c>
       <c r="P17" t="s">
-        <v>457</v>
+        <v>512</v>
       </c>
       <c r="Q17" t="s">
         <v>214</v>
@@ -2561,13 +2737,13 @@
     </row>
     <row r="18" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E18">
         <v>0.41107500000000002</v>
@@ -2585,7 +2761,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -2597,10 +2773,10 @@
         <v>212</v>
       </c>
       <c r="O18" t="s">
-        <v>344</v>
+        <v>397</v>
       </c>
       <c r="P18" t="s">
-        <v>458</v>
+        <v>513</v>
       </c>
       <c r="Q18" t="s">
         <v>214</v>
@@ -2617,13 +2793,13 @@
     </row>
     <row r="19" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="C19" t="s">
         <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E19">
         <v>0.41107500000000002</v>
@@ -2641,7 +2817,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -2653,10 +2829,10 @@
         <v>212</v>
       </c>
       <c r="O19" t="s">
-        <v>345</v>
+        <v>398</v>
       </c>
       <c r="P19" t="s">
-        <v>459</v>
+        <v>514</v>
       </c>
       <c r="Q19" t="s">
         <v>214</v>
@@ -2673,7 +2849,7 @@
     </row>
     <row r="20" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="C20" t="s">
         <v>13</v>
@@ -2697,7 +2873,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K20">
         <v>1</v>
@@ -2709,10 +2885,10 @@
         <v>212</v>
       </c>
       <c r="O20" t="s">
-        <v>346</v>
+        <v>399</v>
       </c>
       <c r="P20" t="s">
-        <v>460</v>
+        <v>515</v>
       </c>
       <c r="Q20" t="s">
         <v>214</v>
@@ -2729,16 +2905,16 @@
     </row>
     <row r="21" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E21">
-        <v>0.38626874999999999</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F21">
         <v>1365</v>
@@ -2753,7 +2929,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J21" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -2765,10 +2941,10 @@
         <v>212</v>
       </c>
       <c r="O21" t="s">
-        <v>347</v>
+        <v>400</v>
       </c>
       <c r="P21" t="s">
-        <v>461</v>
+        <v>516</v>
       </c>
       <c r="Q21" t="s">
         <v>214</v>
@@ -2785,16 +2961,16 @@
     </row>
     <row r="22" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E22">
-        <v>0.38626874999999999</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F22">
         <v>1365</v>
@@ -2809,7 +2985,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -2821,10 +2997,10 @@
         <v>212</v>
       </c>
       <c r="O22" t="s">
-        <v>348</v>
+        <v>401</v>
       </c>
       <c r="P22" t="s">
-        <v>462</v>
+        <v>517</v>
       </c>
       <c r="Q22" t="s">
         <v>214</v>
@@ -2841,7 +3017,7 @@
     </row>
     <row r="23" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -2865,7 +3041,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -2877,10 +3053,10 @@
         <v>212</v>
       </c>
       <c r="O23" t="s">
-        <v>349</v>
+        <v>402</v>
       </c>
       <c r="P23" t="s">
-        <v>463</v>
+        <v>518</v>
       </c>
       <c r="Q23" t="s">
         <v>214</v>
@@ -2897,16 +3073,16 @@
     </row>
     <row r="24" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E24">
-        <v>0.42525000000000007</v>
+        <v>0.38626874999999999</v>
       </c>
       <c r="F24">
         <v>1365</v>
@@ -2921,7 +3097,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="K24">
         <v>1</v>
@@ -2933,10 +3109,10 @@
         <v>212</v>
       </c>
       <c r="O24" t="s">
-        <v>350</v>
+        <v>403</v>
       </c>
       <c r="P24" t="s">
-        <v>464</v>
+        <v>519</v>
       </c>
       <c r="Q24" t="s">
         <v>214</v>
@@ -2953,16 +3129,16 @@
     </row>
     <row r="25" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E25">
-        <v>0.42525000000000007</v>
+        <v>0.38626874999999999</v>
       </c>
       <c r="F25">
         <v>1365</v>
@@ -2977,7 +3153,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J25" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K25">
         <v>1</v>
@@ -2989,10 +3165,10 @@
         <v>212</v>
       </c>
       <c r="O25" t="s">
-        <v>351</v>
+        <v>404</v>
       </c>
       <c r="P25" t="s">
-        <v>465</v>
+        <v>520</v>
       </c>
       <c r="Q25" t="s">
         <v>214</v>
@@ -3009,16 +3185,16 @@
     </row>
     <row r="26" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E26">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F26">
         <v>1365</v>
@@ -3033,7 +3209,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J26" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="K26">
         <v>1</v>
@@ -3045,10 +3221,10 @@
         <v>212</v>
       </c>
       <c r="O26" t="s">
-        <v>352</v>
+        <v>405</v>
       </c>
       <c r="P26" t="s">
-        <v>466</v>
+        <v>521</v>
       </c>
       <c r="Q26" t="s">
         <v>214</v>
@@ -3065,16 +3241,16 @@
     </row>
     <row r="27" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
       </c>
       <c r="D27" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E27">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F27">
         <v>1365</v>
@@ -3089,7 +3265,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -3101,10 +3277,10 @@
         <v>212</v>
       </c>
       <c r="O27" t="s">
-        <v>353</v>
+        <v>406</v>
       </c>
       <c r="P27" t="s">
-        <v>467</v>
+        <v>522</v>
       </c>
       <c r="Q27" t="s">
         <v>214</v>
@@ -3121,7 +3297,7 @@
     </row>
     <row r="28" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -3145,7 +3321,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -3157,10 +3333,10 @@
         <v>212</v>
       </c>
       <c r="O28" t="s">
-        <v>354</v>
+        <v>407</v>
       </c>
       <c r="P28" t="s">
-        <v>468</v>
+        <v>523</v>
       </c>
       <c r="Q28" t="s">
         <v>214</v>
@@ -3177,16 +3353,16 @@
     </row>
     <row r="29" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>355</v>
+        <v>408</v>
       </c>
       <c r="C29" t="s">
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E29">
-        <v>0.42524999999999996</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F29">
         <v>1365</v>
@@ -3201,7 +3377,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J29" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K29">
         <v>1</v>
@@ -3213,10 +3389,10 @@
         <v>212</v>
       </c>
       <c r="O29" t="s">
-        <v>355</v>
+        <v>408</v>
       </c>
       <c r="P29" t="s">
-        <v>469</v>
+        <v>524</v>
       </c>
       <c r="Q29" t="s">
         <v>214</v>
@@ -3233,16 +3409,16 @@
     </row>
     <row r="30" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="C30" t="s">
         <v>13</v>
       </c>
       <c r="D30" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E30">
-        <v>0.42525000000000007</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F30">
         <v>1365</v>
@@ -3257,7 +3433,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J30" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="K30">
         <v>1</v>
@@ -3269,10 +3445,10 @@
         <v>212</v>
       </c>
       <c r="O30" t="s">
-        <v>356</v>
+        <v>409</v>
       </c>
       <c r="P30" t="s">
-        <v>470</v>
+        <v>525</v>
       </c>
       <c r="Q30" t="s">
         <v>214</v>
@@ -3289,7 +3465,7 @@
     </row>
     <row r="31" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="C31" t="s">
         <v>13</v>
@@ -3298,7 +3474,7 @@
         <v>39</v>
       </c>
       <c r="E31">
-        <v>0.42525000000000007</v>
+        <v>0.42524999999999996</v>
       </c>
       <c r="F31">
         <v>1365</v>
@@ -3313,7 +3489,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J31" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -3325,10 +3501,10 @@
         <v>212</v>
       </c>
       <c r="O31" t="s">
-        <v>357</v>
+        <v>410</v>
       </c>
       <c r="P31" t="s">
-        <v>471</v>
+        <v>526</v>
       </c>
       <c r="Q31" t="s">
         <v>214</v>
@@ -3345,16 +3521,16 @@
     </row>
     <row r="32" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="C32" t="s">
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E32">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F32">
         <v>1365</v>
@@ -3369,7 +3545,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -3381,10 +3557,10 @@
         <v>212</v>
       </c>
       <c r="O32" t="s">
-        <v>358</v>
+        <v>411</v>
       </c>
       <c r="P32" t="s">
-        <v>472</v>
+        <v>527</v>
       </c>
       <c r="Q32" t="s">
         <v>214</v>
@@ -3401,16 +3577,16 @@
     </row>
     <row r="33" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="C33" t="s">
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E33">
-        <v>0.41107500000000002</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F33">
         <v>1365</v>
@@ -3425,7 +3601,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J33" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -3437,10 +3613,10 @@
         <v>212</v>
       </c>
       <c r="O33" t="s">
-        <v>359</v>
+        <v>412</v>
       </c>
       <c r="P33" t="s">
-        <v>473</v>
+        <v>528</v>
       </c>
       <c r="Q33" t="s">
         <v>214</v>
@@ -3457,7 +3633,7 @@
     </row>
     <row r="34" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -3481,7 +3657,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J34" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K34">
         <v>1</v>
@@ -3493,10 +3669,10 @@
         <v>212</v>
       </c>
       <c r="O34" t="s">
-        <v>360</v>
+        <v>413</v>
       </c>
       <c r="P34" t="s">
-        <v>474</v>
+        <v>529</v>
       </c>
       <c r="Q34" t="s">
         <v>214</v>
@@ -3513,16 +3689,16 @@
     </row>
     <row r="35" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E35">
-        <v>0.38626875000000005</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F35">
         <v>1365</v>
@@ -3537,7 +3713,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -3549,10 +3725,10 @@
         <v>212</v>
       </c>
       <c r="O35" t="s">
-        <v>361</v>
+        <v>414</v>
       </c>
       <c r="P35" t="s">
-        <v>475</v>
+        <v>530</v>
       </c>
       <c r="Q35" t="s">
         <v>214</v>
@@ -3569,16 +3745,16 @@
     </row>
     <row r="36" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>362</v>
+        <v>415</v>
       </c>
       <c r="C36" t="s">
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E36">
-        <v>0.38626875000000005</v>
+        <v>0.41107500000000002</v>
       </c>
       <c r="F36">
         <v>1365</v>
@@ -3593,7 +3769,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J36" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -3605,10 +3781,10 @@
         <v>212</v>
       </c>
       <c r="O36" t="s">
-        <v>362</v>
+        <v>415</v>
       </c>
       <c r="P36" t="s">
-        <v>476</v>
+        <v>531</v>
       </c>
       <c r="Q36" t="s">
         <v>214</v>
@@ -3625,16 +3801,16 @@
     </row>
     <row r="37" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
       </c>
       <c r="D37" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E37">
-        <v>0.39690000000000014</v>
+        <v>0.38626875000000005</v>
       </c>
       <c r="F37">
         <v>1365</v>
@@ -3649,7 +3825,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J37" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="K37">
         <v>1</v>
@@ -3661,10 +3837,10 @@
         <v>212</v>
       </c>
       <c r="O37" t="s">
-        <v>363</v>
+        <v>416</v>
       </c>
       <c r="P37" t="s">
-        <v>477</v>
+        <v>532</v>
       </c>
       <c r="Q37" t="s">
         <v>214</v>
@@ -3681,16 +3857,16 @@
     </row>
     <row r="38" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="C38" t="s">
         <v>13</v>
       </c>
       <c r="D38" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E38">
-        <v>0.39690000000000014</v>
+        <v>0.38626875000000005</v>
       </c>
       <c r="F38">
         <v>1365</v>
@@ -3705,7 +3881,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J38" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="K38">
         <v>1</v>
@@ -3717,10 +3893,10 @@
         <v>212</v>
       </c>
       <c r="O38" t="s">
-        <v>364</v>
+        <v>417</v>
       </c>
       <c r="P38" t="s">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="Q38" t="s">
         <v>214</v>
@@ -3737,16 +3913,16 @@
     </row>
     <row r="39" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="E39">
-        <v>0.42525000000000007</v>
+        <v>0.39690000000000014</v>
       </c>
       <c r="F39">
         <v>1365</v>
@@ -3761,7 +3937,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -3773,10 +3949,10 @@
         <v>212</v>
       </c>
       <c r="O39" t="s">
-        <v>365</v>
+        <v>418</v>
       </c>
       <c r="P39" t="s">
-        <v>479</v>
+        <v>534</v>
       </c>
       <c r="Q39" t="s">
         <v>214</v>
@@ -3793,16 +3969,16 @@
     </row>
     <row r="40" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="C40" t="s">
         <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E40">
-        <v>0.21971250000000006</v>
+        <v>0.39690000000000014</v>
       </c>
       <c r="F40">
         <v>1365</v>
@@ -3817,7 +3993,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -3829,10 +4005,10 @@
         <v>212</v>
       </c>
       <c r="O40" t="s">
-        <v>366</v>
+        <v>419</v>
       </c>
       <c r="P40" t="s">
-        <v>480</v>
+        <v>535</v>
       </c>
       <c r="Q40" t="s">
         <v>214</v>
@@ -3849,16 +4025,16 @@
     </row>
     <row r="41" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E41">
-        <v>0.21971250000000006</v>
+        <v>0.42525000000000007</v>
       </c>
       <c r="F41">
         <v>1365</v>
@@ -3873,7 +4049,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J41" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="K41">
         <v>1</v>
@@ -3885,10 +4061,10 @@
         <v>212</v>
       </c>
       <c r="O41" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="P41" t="s">
-        <v>481</v>
+        <v>536</v>
       </c>
       <c r="Q41" t="s">
         <v>214</v>
@@ -3905,13 +4081,13 @@
     </row>
     <row r="42" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42">
         <v>0.21971250000000006</v>
@@ -3929,7 +4105,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J42" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -3941,10 +4117,10 @@
         <v>212</v>
       </c>
       <c r="O42" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="P42" t="s">
-        <v>482</v>
+        <v>537</v>
       </c>
       <c r="Q42" t="s">
         <v>214</v>
@@ -3961,7 +4137,7 @@
     </row>
     <row r="43" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -3985,7 +4161,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J43" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -3997,10 +4173,10 @@
         <v>212</v>
       </c>
       <c r="O43" t="s">
-        <v>369</v>
+        <v>422</v>
       </c>
       <c r="P43" t="s">
-        <v>483</v>
+        <v>538</v>
       </c>
       <c r="Q43" t="s">
         <v>214</v>
@@ -4017,7 +4193,7 @@
     </row>
     <row r="44" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B44" t="s">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -4041,7 +4217,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J44" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K44">
         <v>1</v>
@@ -4053,10 +4229,10 @@
         <v>212</v>
       </c>
       <c r="O44" t="s">
-        <v>370</v>
+        <v>423</v>
       </c>
       <c r="P44" t="s">
-        <v>484</v>
+        <v>539</v>
       </c>
       <c r="Q44" t="s">
         <v>214</v>
@@ -4073,7 +4249,7 @@
     </row>
     <row r="45" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B45" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="C45" t="s">
         <v>13</v>
@@ -4082,7 +4258,7 @@
         <v>56</v>
       </c>
       <c r="E45">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F45">
         <v>1365</v>
@@ -4097,7 +4273,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J45" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K45">
         <v>1</v>
@@ -4109,10 +4285,10 @@
         <v>212</v>
       </c>
       <c r="O45" t="s">
-        <v>371</v>
+        <v>424</v>
       </c>
       <c r="P45" t="s">
-        <v>485</v>
+        <v>540</v>
       </c>
       <c r="Q45" t="s">
         <v>214</v>
@@ -4129,7 +4305,7 @@
     </row>
     <row r="46" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B46" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="C46" t="s">
         <v>13</v>
@@ -4138,7 +4314,7 @@
         <v>56</v>
       </c>
       <c r="E46">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F46">
         <v>1365</v>
@@ -4153,7 +4329,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J46" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K46">
         <v>1</v>
@@ -4165,10 +4341,10 @@
         <v>212</v>
       </c>
       <c r="O46" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="P46" t="s">
-        <v>486</v>
+        <v>541</v>
       </c>
       <c r="Q46" t="s">
         <v>214</v>
@@ -4185,16 +4361,16 @@
     </row>
     <row r="47" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B47" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E47">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F47">
         <v>1365</v>
@@ -4209,7 +4385,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K47">
         <v>1</v>
@@ -4221,10 +4397,10 @@
         <v>212</v>
       </c>
       <c r="O47" t="s">
-        <v>373</v>
+        <v>426</v>
       </c>
       <c r="P47" t="s">
-        <v>487</v>
+        <v>542</v>
       </c>
       <c r="Q47" t="s">
         <v>214</v>
@@ -4241,16 +4417,16 @@
     </row>
     <row r="48" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B48" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="C48" t="s">
         <v>13</v>
       </c>
       <c r="D48" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="E48">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F48">
         <v>1365</v>
@@ -4265,7 +4441,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K48">
         <v>1</v>
@@ -4277,10 +4453,10 @@
         <v>212</v>
       </c>
       <c r="O48" t="s">
-        <v>374</v>
+        <v>427</v>
       </c>
       <c r="P48" t="s">
-        <v>488</v>
+        <v>543</v>
       </c>
       <c r="Q48" t="s">
         <v>214</v>
@@ -4297,13 +4473,13 @@
     </row>
     <row r="49" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B49" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E49">
         <v>0.21971250000000006</v>
@@ -4321,7 +4497,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J49" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K49">
         <v>1</v>
@@ -4333,10 +4509,10 @@
         <v>212</v>
       </c>
       <c r="O49" t="s">
-        <v>375</v>
+        <v>428</v>
       </c>
       <c r="P49" t="s">
-        <v>489</v>
+        <v>544</v>
       </c>
       <c r="Q49" t="s">
         <v>214</v>
@@ -4353,13 +4529,13 @@
     </row>
     <row r="50" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B50" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="C50" t="s">
         <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="E50">
         <v>0.21971250000000006</v>
@@ -4377,7 +4553,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J50" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K50">
         <v>1</v>
@@ -4389,10 +4565,10 @@
         <v>212</v>
       </c>
       <c r="O50" t="s">
-        <v>376</v>
+        <v>429</v>
       </c>
       <c r="P50" t="s">
-        <v>490</v>
+        <v>545</v>
       </c>
       <c r="Q50" t="s">
         <v>214</v>
@@ -4409,7 +4585,7 @@
     </row>
     <row r="51" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B51" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="C51" t="s">
         <v>13</v>
@@ -4433,7 +4609,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J51" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K51">
         <v>1</v>
@@ -4445,10 +4621,10 @@
         <v>212</v>
       </c>
       <c r="O51" t="s">
-        <v>377</v>
+        <v>430</v>
       </c>
       <c r="P51" t="s">
-        <v>491</v>
+        <v>546</v>
       </c>
       <c r="Q51" t="s">
         <v>214</v>
@@ -4465,16 +4641,16 @@
     </row>
     <row r="52" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B52" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="C52" t="s">
         <v>13</v>
       </c>
       <c r="D52" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E52">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F52">
         <v>1365</v>
@@ -4489,7 +4665,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J52" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K52">
         <v>1</v>
@@ -4501,10 +4677,10 @@
         <v>212</v>
       </c>
       <c r="O52" t="s">
-        <v>378</v>
+        <v>431</v>
       </c>
       <c r="P52" t="s">
-        <v>492</v>
+        <v>547</v>
       </c>
       <c r="Q52" t="s">
         <v>214</v>
@@ -4521,16 +4697,16 @@
     </row>
     <row r="53" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B53" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="C53" t="s">
         <v>13</v>
       </c>
       <c r="D53" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E53">
-        <v>0.18781875000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F53">
         <v>1365</v>
@@ -4545,7 +4721,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J53" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K53">
         <v>1</v>
@@ -4557,10 +4733,10 @@
         <v>212</v>
       </c>
       <c r="O53" t="s">
-        <v>379</v>
+        <v>432</v>
       </c>
       <c r="P53" t="s">
-        <v>493</v>
+        <v>548</v>
       </c>
       <c r="Q53" t="s">
         <v>214</v>
@@ -4577,7 +4753,7 @@
     </row>
     <row r="54" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B54" t="s">
-        <v>380</v>
+        <v>433</v>
       </c>
       <c r="C54" t="s">
         <v>13</v>
@@ -4586,7 +4762,7 @@
         <v>69</v>
       </c>
       <c r="E54">
-        <v>0.18781875000000001</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F54">
         <v>1365</v>
@@ -4601,7 +4777,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J54" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K54">
         <v>1</v>
@@ -4613,10 +4789,10 @@
         <v>212</v>
       </c>
       <c r="O54" t="s">
-        <v>380</v>
+        <v>433</v>
       </c>
       <c r="P54" t="s">
-        <v>494</v>
+        <v>549</v>
       </c>
       <c r="Q54" t="s">
         <v>214</v>
@@ -4633,7 +4809,7 @@
     </row>
     <row r="55" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B55" t="s">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="C55" t="s">
         <v>13</v>
@@ -4657,7 +4833,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="K55">
         <v>1</v>
@@ -4669,10 +4845,10 @@
         <v>212</v>
       </c>
       <c r="O55" t="s">
-        <v>381</v>
+        <v>434</v>
       </c>
       <c r="P55" t="s">
-        <v>495</v>
+        <v>550</v>
       </c>
       <c r="Q55" t="s">
         <v>214</v>
@@ -4689,7 +4865,7 @@
     </row>
     <row r="56" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B56" t="s">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -4698,7 +4874,7 @@
         <v>69</v>
       </c>
       <c r="E56">
-        <v>0.21971250000000006</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F56">
         <v>1365</v>
@@ -4713,7 +4889,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K56">
         <v>1</v>
@@ -4725,10 +4901,10 @@
         <v>212</v>
       </c>
       <c r="O56" t="s">
-        <v>382</v>
+        <v>435</v>
       </c>
       <c r="P56" t="s">
-        <v>496</v>
+        <v>551</v>
       </c>
       <c r="Q56" t="s">
         <v>214</v>
@@ -4745,7 +4921,7 @@
     </row>
     <row r="57" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B57" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="C57" t="s">
         <v>13</v>
@@ -4754,7 +4930,7 @@
         <v>69</v>
       </c>
       <c r="E57">
-        <v>0.21971250000000006</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F57">
         <v>1365</v>
@@ -4769,7 +4945,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K57">
         <v>1</v>
@@ -4781,10 +4957,10 @@
         <v>212</v>
       </c>
       <c r="O57" t="s">
-        <v>383</v>
+        <v>436</v>
       </c>
       <c r="P57" t="s">
-        <v>497</v>
+        <v>552</v>
       </c>
       <c r="Q57" t="s">
         <v>214</v>
@@ -4801,7 +4977,7 @@
     </row>
     <row r="58" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B58" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="C58" t="s">
         <v>13</v>
@@ -4825,7 +5001,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J58" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K58">
         <v>1</v>
@@ -4837,10 +5013,10 @@
         <v>212</v>
       </c>
       <c r="O58" t="s">
-        <v>384</v>
+        <v>437</v>
       </c>
       <c r="P58" t="s">
-        <v>498</v>
+        <v>553</v>
       </c>
       <c r="Q58" t="s">
         <v>214</v>
@@ -4857,7 +5033,7 @@
     </row>
     <row r="59" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B59" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="C59" t="s">
         <v>13</v>
@@ -4866,7 +5042,7 @@
         <v>69</v>
       </c>
       <c r="E59">
-        <v>0.1771875</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F59">
         <v>1365</v>
@@ -4881,7 +5057,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K59">
         <v>1</v>
@@ -4893,10 +5069,10 @@
         <v>212</v>
       </c>
       <c r="O59" t="s">
-        <v>385</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s">
-        <v>499</v>
+        <v>554</v>
       </c>
       <c r="Q59" t="s">
         <v>214</v>
@@ -4913,7 +5089,7 @@
     </row>
     <row r="60" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B60" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="C60" t="s">
         <v>13</v>
@@ -4922,7 +5098,7 @@
         <v>69</v>
       </c>
       <c r="E60">
-        <v>0.1771875</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F60">
         <v>1365</v>
@@ -4937,7 +5113,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K60">
         <v>1</v>
@@ -4949,10 +5125,10 @@
         <v>212</v>
       </c>
       <c r="O60" t="s">
-        <v>386</v>
+        <v>439</v>
       </c>
       <c r="P60" t="s">
-        <v>500</v>
+        <v>555</v>
       </c>
       <c r="Q60" t="s">
         <v>214</v>
@@ -4969,7 +5145,7 @@
     </row>
     <row r="61" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B61" t="s">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="C61" t="s">
         <v>13</v>
@@ -4978,7 +5154,7 @@
         <v>69</v>
       </c>
       <c r="E61">
-        <v>0.21971250000000006</v>
+        <v>0.1771875</v>
       </c>
       <c r="F61">
         <v>1365</v>
@@ -4993,7 +5169,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K61">
         <v>1</v>
@@ -5005,10 +5181,10 @@
         <v>212</v>
       </c>
       <c r="O61" t="s">
-        <v>387</v>
+        <v>440</v>
       </c>
       <c r="P61" t="s">
-        <v>501</v>
+        <v>556</v>
       </c>
       <c r="Q61" t="s">
         <v>214</v>
@@ -5025,7 +5201,7 @@
     </row>
     <row r="62" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B62" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="C62" t="s">
         <v>13</v>
@@ -5034,7 +5210,7 @@
         <v>69</v>
       </c>
       <c r="E62">
-        <v>0.20553750000000001</v>
+        <v>0.1771875</v>
       </c>
       <c r="F62">
         <v>1365</v>
@@ -5049,7 +5225,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J62" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K62">
         <v>1</v>
@@ -5061,10 +5237,10 @@
         <v>212</v>
       </c>
       <c r="O62" t="s">
-        <v>388</v>
+        <v>441</v>
       </c>
       <c r="P62" t="s">
-        <v>502</v>
+        <v>557</v>
       </c>
       <c r="Q62" t="s">
         <v>214</v>
@@ -5081,7 +5257,7 @@
     </row>
     <row r="63" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B63" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -5090,7 +5266,7 @@
         <v>69</v>
       </c>
       <c r="E63">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F63">
         <v>1365</v>
@@ -5105,7 +5281,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J63" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K63">
         <v>1</v>
@@ -5117,10 +5293,10 @@
         <v>212</v>
       </c>
       <c r="O63" t="s">
-        <v>389</v>
+        <v>442</v>
       </c>
       <c r="P63" t="s">
-        <v>503</v>
+        <v>558</v>
       </c>
       <c r="Q63" t="s">
         <v>214</v>
@@ -5137,7 +5313,7 @@
     </row>
     <row r="64" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B64" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="C64" t="s">
         <v>13</v>
@@ -5161,7 +5337,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J64" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K64">
         <v>1</v>
@@ -5173,10 +5349,10 @@
         <v>212</v>
       </c>
       <c r="O64" t="s">
-        <v>390</v>
+        <v>443</v>
       </c>
       <c r="P64" t="s">
-        <v>504</v>
+        <v>559</v>
       </c>
       <c r="Q64" t="s">
         <v>214</v>
@@ -5193,13 +5369,13 @@
     </row>
     <row r="65" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B65" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="C65" t="s">
         <v>13</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E65">
         <v>0.20553750000000001</v>
@@ -5217,7 +5393,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J65" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K65">
         <v>1</v>
@@ -5229,10 +5405,10 @@
         <v>212</v>
       </c>
       <c r="O65" t="s">
-        <v>391</v>
+        <v>444</v>
       </c>
       <c r="P65" t="s">
-        <v>505</v>
+        <v>560</v>
       </c>
       <c r="Q65" t="s">
         <v>214</v>
@@ -5249,13 +5425,13 @@
     </row>
     <row r="66" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B66" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="C66" t="s">
         <v>13</v>
       </c>
       <c r="D66" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E66">
         <v>0.20553750000000001</v>
@@ -5273,7 +5449,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J66" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K66">
         <v>1</v>
@@ -5285,10 +5461,10 @@
         <v>212</v>
       </c>
       <c r="O66" t="s">
-        <v>392</v>
+        <v>445</v>
       </c>
       <c r="P66" t="s">
-        <v>506</v>
+        <v>561</v>
       </c>
       <c r="Q66" t="s">
         <v>214</v>
@@ -5305,13 +5481,13 @@
     </row>
     <row r="67" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B67" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
       <c r="C67" t="s">
         <v>13</v>
       </c>
       <c r="D67" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E67">
         <v>0.20553750000000001</v>
@@ -5329,7 +5505,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J67" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K67">
         <v>1</v>
@@ -5341,10 +5517,10 @@
         <v>212</v>
       </c>
       <c r="O67" t="s">
-        <v>393</v>
+        <v>446</v>
       </c>
       <c r="P67" t="s">
-        <v>507</v>
+        <v>562</v>
       </c>
       <c r="Q67" t="s">
         <v>214</v>
@@ -5361,13 +5537,13 @@
     </row>
     <row r="68" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B68" t="s">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="C68" t="s">
         <v>13</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E68">
         <v>0.20553750000000001</v>
@@ -5385,7 +5561,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J68" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="K68">
         <v>1</v>
@@ -5397,10 +5573,10 @@
         <v>212</v>
       </c>
       <c r="O68" t="s">
-        <v>394</v>
+        <v>447</v>
       </c>
       <c r="P68" t="s">
-        <v>508</v>
+        <v>563</v>
       </c>
       <c r="Q68" t="s">
         <v>214</v>
@@ -5417,13 +5593,13 @@
     </row>
     <row r="69" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B69" t="s">
-        <v>395</v>
+        <v>448</v>
       </c>
       <c r="C69" t="s">
         <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E69">
         <v>0.20553750000000001</v>
@@ -5441,7 +5617,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J69" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="K69">
         <v>1</v>
@@ -5453,10 +5629,10 @@
         <v>212</v>
       </c>
       <c r="O69" t="s">
-        <v>395</v>
+        <v>448</v>
       </c>
       <c r="P69" t="s">
-        <v>509</v>
+        <v>564</v>
       </c>
       <c r="Q69" t="s">
         <v>214</v>
@@ -5473,13 +5649,13 @@
     </row>
     <row r="70" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B70" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
       </c>
       <c r="D70" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E70">
         <v>0.20553750000000001</v>
@@ -5497,7 +5673,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J70" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="K70">
         <v>1</v>
@@ -5509,10 +5685,10 @@
         <v>212</v>
       </c>
       <c r="O70" t="s">
-        <v>396</v>
+        <v>449</v>
       </c>
       <c r="P70" t="s">
-        <v>510</v>
+        <v>565</v>
       </c>
       <c r="Q70" t="s">
         <v>214</v>
@@ -5529,7 +5705,7 @@
     </row>
     <row r="71" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B71" t="s">
-        <v>397</v>
+        <v>450</v>
       </c>
       <c r="C71" t="s">
         <v>13</v>
@@ -5538,7 +5714,7 @@
         <v>89</v>
       </c>
       <c r="E71">
-        <v>0.1771875</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F71">
         <v>1365</v>
@@ -5553,7 +5729,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J71" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K71">
         <v>1</v>
@@ -5565,10 +5741,10 @@
         <v>212</v>
       </c>
       <c r="O71" t="s">
-        <v>397</v>
+        <v>450</v>
       </c>
       <c r="P71" t="s">
-        <v>511</v>
+        <v>566</v>
       </c>
       <c r="Q71" t="s">
         <v>214</v>
@@ -5585,7 +5761,7 @@
     </row>
     <row r="72" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B72" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="C72" t="s">
         <v>13</v>
@@ -5594,7 +5770,7 @@
         <v>89</v>
       </c>
       <c r="E72">
-        <v>0.1771875</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F72">
         <v>1365</v>
@@ -5609,7 +5785,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J72" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K72">
         <v>1</v>
@@ -5621,10 +5797,10 @@
         <v>212</v>
       </c>
       <c r="O72" t="s">
-        <v>398</v>
+        <v>451</v>
       </c>
       <c r="P72" t="s">
-        <v>512</v>
+        <v>567</v>
       </c>
       <c r="Q72" t="s">
         <v>214</v>
@@ -5641,7 +5817,7 @@
     </row>
     <row r="73" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B73" t="s">
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="C73" t="s">
         <v>13</v>
@@ -5650,7 +5826,7 @@
         <v>89</v>
       </c>
       <c r="E73">
-        <v>0.18781875000000001</v>
+        <v>0.1771875</v>
       </c>
       <c r="F73">
         <v>1365</v>
@@ -5665,7 +5841,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J73" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K73">
         <v>1</v>
@@ -5677,10 +5853,10 @@
         <v>212</v>
       </c>
       <c r="O73" t="s">
-        <v>399</v>
+        <v>452</v>
       </c>
       <c r="P73" t="s">
-        <v>513</v>
+        <v>568</v>
       </c>
       <c r="Q73" t="s">
         <v>214</v>
@@ -5697,16 +5873,16 @@
     </row>
     <row r="74" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B74" t="s">
-        <v>400</v>
+        <v>453</v>
       </c>
       <c r="C74" t="s">
         <v>13</v>
       </c>
       <c r="D74" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E74">
-        <v>0.20553750000000001</v>
+        <v>0.1771875</v>
       </c>
       <c r="F74">
         <v>1365</v>
@@ -5721,7 +5897,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J74" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K74">
         <v>1</v>
@@ -5733,10 +5909,10 @@
         <v>212</v>
       </c>
       <c r="O74" t="s">
-        <v>400</v>
+        <v>453</v>
       </c>
       <c r="P74" t="s">
-        <v>514</v>
+        <v>569</v>
       </c>
       <c r="Q74" t="s">
         <v>214</v>
@@ -5753,16 +5929,16 @@
     </row>
     <row r="75" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B75" t="s">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="C75" t="s">
         <v>13</v>
       </c>
       <c r="D75" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E75">
-        <v>0.20553750000000001</v>
+        <v>0.18781875000000001</v>
       </c>
       <c r="F75">
         <v>1365</v>
@@ -5777,7 +5953,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J75" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K75">
         <v>1</v>
@@ -5789,10 +5965,10 @@
         <v>212</v>
       </c>
       <c r="O75" t="s">
-        <v>401</v>
+        <v>454</v>
       </c>
       <c r="P75" t="s">
-        <v>515</v>
+        <v>570</v>
       </c>
       <c r="Q75" t="s">
         <v>214</v>
@@ -5809,7 +5985,7 @@
     </row>
     <row r="76" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B76" t="s">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="C76" t="s">
         <v>13</v>
@@ -5833,7 +6009,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J76" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K76">
         <v>1</v>
@@ -5845,10 +6021,10 @@
         <v>212</v>
       </c>
       <c r="O76" t="s">
-        <v>402</v>
+        <v>455</v>
       </c>
       <c r="P76" t="s">
-        <v>516</v>
+        <v>571</v>
       </c>
       <c r="Q76" t="s">
         <v>214</v>
@@ -5865,7 +6041,7 @@
     </row>
     <row r="77" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B77" t="s">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
@@ -5889,7 +6065,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -5901,10 +6077,10 @@
         <v>212</v>
       </c>
       <c r="O77" t="s">
-        <v>403</v>
+        <v>456</v>
       </c>
       <c r="P77" t="s">
-        <v>517</v>
+        <v>572</v>
       </c>
       <c r="Q77" t="s">
         <v>214</v>
@@ -5921,16 +6097,16 @@
     </row>
     <row r="78" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B78" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="C78" t="s">
         <v>13</v>
       </c>
       <c r="D78" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E78">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F78">
         <v>1365</v>
@@ -5945,7 +6121,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J78" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K78">
         <v>1</v>
@@ -5957,10 +6133,10 @@
         <v>212</v>
       </c>
       <c r="O78" t="s">
-        <v>404</v>
+        <v>457</v>
       </c>
       <c r="P78" t="s">
-        <v>518</v>
+        <v>573</v>
       </c>
       <c r="Q78" t="s">
         <v>214</v>
@@ -5977,16 +6153,16 @@
     </row>
     <row r="79" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B79" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="C79" t="s">
         <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E79">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F79">
         <v>1365</v>
@@ -6001,7 +6177,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J79" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K79">
         <v>1</v>
@@ -6013,10 +6189,10 @@
         <v>212</v>
       </c>
       <c r="O79" t="s">
-        <v>405</v>
+        <v>458</v>
       </c>
       <c r="P79" t="s">
-        <v>519</v>
+        <v>574</v>
       </c>
       <c r="Q79" t="s">
         <v>214</v>
@@ -6033,7 +6209,7 @@
     </row>
     <row r="80" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B80" t="s">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="C80" t="s">
         <v>13</v>
@@ -6057,7 +6233,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J80" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K80">
         <v>1</v>
@@ -6069,10 +6245,10 @@
         <v>212</v>
       </c>
       <c r="O80" t="s">
-        <v>406</v>
+        <v>459</v>
       </c>
       <c r="P80" t="s">
-        <v>520</v>
+        <v>575</v>
       </c>
       <c r="Q80" t="s">
         <v>214</v>
@@ -6089,13 +6265,13 @@
     </row>
     <row r="81" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B81" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="C81" t="s">
         <v>13</v>
       </c>
       <c r="D81" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="E81">
         <v>0.21971250000000006</v>
@@ -6113,7 +6289,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J81" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K81">
         <v>1</v>
@@ -6125,10 +6301,10 @@
         <v>212</v>
       </c>
       <c r="O81" t="s">
-        <v>407</v>
+        <v>460</v>
       </c>
       <c r="P81" t="s">
-        <v>521</v>
+        <v>576</v>
       </c>
       <c r="Q81" t="s">
         <v>214</v>
@@ -6145,13 +6321,13 @@
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B82" t="s">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="C82" t="s">
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="E82">
         <v>0.21971250000000006</v>
@@ -6169,7 +6345,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -6181,10 +6357,10 @@
         <v>212</v>
       </c>
       <c r="O82" t="s">
-        <v>408</v>
+        <v>461</v>
       </c>
       <c r="P82" t="s">
-        <v>522</v>
+        <v>577</v>
       </c>
       <c r="Q82" t="s">
         <v>214</v>
@@ -6201,16 +6377,16 @@
     </row>
     <row r="83" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B83" t="s">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="C83" t="s">
         <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E83">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F83">
         <v>1365</v>
@@ -6225,7 +6401,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J83" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K83">
         <v>1</v>
@@ -6237,10 +6413,10 @@
         <v>212</v>
       </c>
       <c r="O83" t="s">
-        <v>409</v>
+        <v>462</v>
       </c>
       <c r="P83" t="s">
-        <v>523</v>
+        <v>578</v>
       </c>
       <c r="Q83" t="s">
         <v>214</v>
@@ -6257,16 +6433,16 @@
     </row>
     <row r="84" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B84" t="s">
-        <v>410</v>
+        <v>463</v>
       </c>
       <c r="C84" t="s">
         <v>13</v>
       </c>
       <c r="D84" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="E84">
-        <v>0.20553750000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F84">
         <v>1365</v>
@@ -6281,7 +6457,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J84" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K84">
         <v>1</v>
@@ -6293,10 +6469,10 @@
         <v>212</v>
       </c>
       <c r="O84" t="s">
-        <v>410</v>
+        <v>463</v>
       </c>
       <c r="P84" t="s">
-        <v>524</v>
+        <v>579</v>
       </c>
       <c r="Q84" t="s">
         <v>214</v>
@@ -6313,7 +6489,7 @@
     </row>
     <row r="85" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B85" t="s">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="C85" t="s">
         <v>13</v>
@@ -6337,7 +6513,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J85" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="K85">
         <v>1</v>
@@ -6349,10 +6525,10 @@
         <v>212</v>
       </c>
       <c r="O85" t="s">
-        <v>411</v>
+        <v>464</v>
       </c>
       <c r="P85" t="s">
-        <v>525</v>
+        <v>580</v>
       </c>
       <c r="Q85" t="s">
         <v>214</v>
@@ -6369,16 +6545,16 @@
     </row>
     <row r="86" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B86" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="C86" t="s">
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="E86">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F86">
         <v>1365</v>
@@ -6393,7 +6569,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J86" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K86">
         <v>1</v>
@@ -6405,10 +6581,10 @@
         <v>212</v>
       </c>
       <c r="O86" t="s">
-        <v>412</v>
+        <v>465</v>
       </c>
       <c r="P86" t="s">
-        <v>526</v>
+        <v>581</v>
       </c>
       <c r="Q86" t="s">
         <v>214</v>
@@ -6425,16 +6601,16 @@
     </row>
     <row r="87" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B87" t="s">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="C87" t="s">
         <v>13</v>
       </c>
       <c r="D87" t="s">
-        <v>50</v>
+        <v>106</v>
       </c>
       <c r="E87">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F87">
         <v>1365</v>
@@ -6449,7 +6625,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J87" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K87">
         <v>1</v>
@@ -6461,10 +6637,10 @@
         <v>212</v>
       </c>
       <c r="O87" t="s">
-        <v>413</v>
+        <v>466</v>
       </c>
       <c r="P87" t="s">
-        <v>527</v>
+        <v>582</v>
       </c>
       <c r="Q87" t="s">
         <v>214</v>
@@ -6481,7 +6657,7 @@
     </row>
     <row r="88" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B88" t="s">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="C88" t="s">
         <v>13</v>
@@ -6505,7 +6681,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J88" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K88">
         <v>1</v>
@@ -6517,10 +6693,10 @@
         <v>212</v>
       </c>
       <c r="O88" t="s">
-        <v>414</v>
+        <v>467</v>
       </c>
       <c r="P88" t="s">
-        <v>528</v>
+        <v>583</v>
       </c>
       <c r="Q88" t="s">
         <v>214</v>
@@ -6537,7 +6713,7 @@
     </row>
     <row r="89" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B89" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="C89" t="s">
         <v>13</v>
@@ -6561,7 +6737,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J89" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -6573,10 +6749,10 @@
         <v>212</v>
       </c>
       <c r="O89" t="s">
-        <v>415</v>
+        <v>468</v>
       </c>
       <c r="P89" t="s">
-        <v>529</v>
+        <v>584</v>
       </c>
       <c r="Q89" t="s">
         <v>214</v>
@@ -6593,7 +6769,7 @@
     </row>
     <row r="90" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B90" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="C90" t="s">
         <v>13</v>
@@ -6617,7 +6793,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J90" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -6629,10 +6805,10 @@
         <v>212</v>
       </c>
       <c r="O90" t="s">
-        <v>416</v>
+        <v>469</v>
       </c>
       <c r="P90" t="s">
-        <v>530</v>
+        <v>585</v>
       </c>
       <c r="Q90" t="s">
         <v>214</v>
@@ -6649,7 +6825,7 @@
     </row>
     <row r="91" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B91" t="s">
-        <v>417</v>
+        <v>470</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
@@ -6658,7 +6834,7 @@
         <v>50</v>
       </c>
       <c r="E91">
-        <v>0.1771875</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F91">
         <v>1365</v>
@@ -6673,7 +6849,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J91" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K91">
         <v>1</v>
@@ -6685,10 +6861,10 @@
         <v>212</v>
       </c>
       <c r="O91" t="s">
-        <v>417</v>
+        <v>470</v>
       </c>
       <c r="P91" t="s">
-        <v>531</v>
+        <v>586</v>
       </c>
       <c r="Q91" t="s">
         <v>214</v>
@@ -6705,7 +6881,7 @@
     </row>
     <row r="92" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B92" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="C92" t="s">
         <v>13</v>
@@ -6714,7 +6890,7 @@
         <v>50</v>
       </c>
       <c r="E92">
-        <v>0.1771875</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F92">
         <v>1365</v>
@@ -6729,7 +6905,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J92" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="K92">
         <v>1</v>
@@ -6741,10 +6917,10 @@
         <v>212</v>
       </c>
       <c r="O92" t="s">
-        <v>418</v>
+        <v>471</v>
       </c>
       <c r="P92" t="s">
-        <v>532</v>
+        <v>587</v>
       </c>
       <c r="Q92" t="s">
         <v>214</v>
@@ -6761,13 +6937,13 @@
     </row>
     <row r="93" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B93" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="C93" t="s">
         <v>13</v>
       </c>
       <c r="D93" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="E93">
         <v>0.1771875</v>
@@ -6785,7 +6961,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J93" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="K93">
         <v>1</v>
@@ -6797,10 +6973,10 @@
         <v>212</v>
       </c>
       <c r="O93" t="s">
-        <v>419</v>
+        <v>472</v>
       </c>
       <c r="P93" t="s">
-        <v>533</v>
+        <v>588</v>
       </c>
       <c r="Q93" t="s">
         <v>214</v>
@@ -6817,13 +6993,13 @@
     </row>
     <row r="94" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B94" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="C94" t="s">
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="E94">
         <v>0.1771875</v>
@@ -6841,7 +7017,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J94" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="K94">
         <v>1</v>
@@ -6853,10 +7029,10 @@
         <v>212</v>
       </c>
       <c r="O94" t="s">
-        <v>420</v>
+        <v>473</v>
       </c>
       <c r="P94" t="s">
-        <v>534</v>
+        <v>589</v>
       </c>
       <c r="Q94" t="s">
         <v>214</v>
@@ -6873,7 +7049,7 @@
     </row>
     <row r="95" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B95" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="C95" t="s">
         <v>13</v>
@@ -6897,7 +7073,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J95" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K95">
         <v>1</v>
@@ -6909,10 +7085,10 @@
         <v>212</v>
       </c>
       <c r="O95" t="s">
-        <v>421</v>
+        <v>474</v>
       </c>
       <c r="P95" t="s">
-        <v>535</v>
+        <v>590</v>
       </c>
       <c r="Q95" t="s">
         <v>214</v>
@@ -6929,16 +7105,16 @@
     </row>
     <row r="96" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B96" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="C96" t="s">
         <v>13</v>
       </c>
       <c r="D96" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E96">
-        <v>0.20553750000000001</v>
+        <v>0.1771875</v>
       </c>
       <c r="F96">
         <v>1365</v>
@@ -6953,7 +7129,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J96" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K96">
         <v>1</v>
@@ -6965,10 +7141,10 @@
         <v>212</v>
       </c>
       <c r="O96" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="P96" t="s">
-        <v>536</v>
+        <v>591</v>
       </c>
       <c r="Q96" t="s">
         <v>214</v>
@@ -6985,16 +7161,16 @@
     </row>
     <row r="97" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B97" t="s">
-        <v>423</v>
+        <v>476</v>
       </c>
       <c r="C97" t="s">
         <v>13</v>
       </c>
       <c r="D97" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E97">
-        <v>0.20553750000000001</v>
+        <v>0.1771875</v>
       </c>
       <c r="F97">
         <v>1365</v>
@@ -7009,7 +7185,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J97" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K97">
         <v>1</v>
@@ -7021,10 +7197,10 @@
         <v>212</v>
       </c>
       <c r="O97" t="s">
-        <v>423</v>
+        <v>476</v>
       </c>
       <c r="P97" t="s">
-        <v>537</v>
+        <v>592</v>
       </c>
       <c r="Q97" t="s">
         <v>214</v>
@@ -7041,13 +7217,13 @@
     </row>
     <row r="98" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B98" t="s">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
       </c>
       <c r="D98" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="E98">
         <v>0.20553750000000001</v>
@@ -7065,7 +7241,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J98" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K98">
         <v>1</v>
@@ -7077,10 +7253,10 @@
         <v>212</v>
       </c>
       <c r="O98" t="s">
-        <v>424</v>
+        <v>477</v>
       </c>
       <c r="P98" t="s">
-        <v>538</v>
+        <v>593</v>
       </c>
       <c r="Q98" t="s">
         <v>214</v>
@@ -7097,13 +7273,13 @@
     </row>
     <row r="99" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B99" t="s">
-        <v>425</v>
+        <v>478</v>
       </c>
       <c r="C99" t="s">
         <v>13</v>
       </c>
       <c r="D99" t="s">
-        <v>17</v>
+        <v>121</v>
       </c>
       <c r="E99">
         <v>0.20553750000000001</v>
@@ -7121,7 +7297,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J99" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K99">
         <v>1</v>
@@ -7133,10 +7309,10 @@
         <v>212</v>
       </c>
       <c r="O99" t="s">
-        <v>425</v>
+        <v>478</v>
       </c>
       <c r="P99" t="s">
-        <v>539</v>
+        <v>594</v>
       </c>
       <c r="Q99" t="s">
         <v>214</v>
@@ -7153,7 +7329,7 @@
     </row>
     <row r="100" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B100" t="s">
-        <v>426</v>
+        <v>479</v>
       </c>
       <c r="C100" t="s">
         <v>13</v>
@@ -7177,7 +7353,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J100" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K100">
         <v>1</v>
@@ -7189,10 +7365,10 @@
         <v>212</v>
       </c>
       <c r="O100" t="s">
-        <v>426</v>
+        <v>479</v>
       </c>
       <c r="P100" t="s">
-        <v>540</v>
+        <v>595</v>
       </c>
       <c r="Q100" t="s">
         <v>214</v>
@@ -7209,16 +7385,16 @@
     </row>
     <row r="101" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B101" t="s">
-        <v>427</v>
+        <v>480</v>
       </c>
       <c r="C101" t="s">
         <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="E101">
-        <v>0.22680000000000003</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F101">
         <v>1365</v>
@@ -7233,7 +7409,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J101" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K101">
         <v>1</v>
@@ -7245,10 +7421,10 @@
         <v>212</v>
       </c>
       <c r="O101" t="s">
-        <v>427</v>
+        <v>480</v>
       </c>
       <c r="P101" t="s">
-        <v>541</v>
+        <v>596</v>
       </c>
       <c r="Q101" t="s">
         <v>214</v>
@@ -7265,16 +7441,16 @@
     </row>
     <row r="102" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B102" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="C102" t="s">
         <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>128</v>
+        <v>17</v>
       </c>
       <c r="E102">
-        <v>0.21971250000000006</v>
+        <v>0.20553750000000001</v>
       </c>
       <c r="F102">
         <v>1365</v>
@@ -7289,7 +7465,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J102" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K102">
         <v>1</v>
@@ -7301,10 +7477,10 @@
         <v>212</v>
       </c>
       <c r="O102" t="s">
-        <v>428</v>
+        <v>481</v>
       </c>
       <c r="P102" t="s">
-        <v>542</v>
+        <v>597</v>
       </c>
       <c r="Q102" t="s">
         <v>214</v>
@@ -7321,16 +7497,16 @@
     </row>
     <row r="103" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B103" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
       <c r="C103" t="s">
         <v>13</v>
       </c>
       <c r="D103" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="E103">
-        <v>0.21971250000000006</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F103">
         <v>1365</v>
@@ -7345,7 +7521,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J103" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K103">
         <v>1</v>
@@ -7357,10 +7533,10 @@
         <v>212</v>
       </c>
       <c r="O103" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
       <c r="P103" t="s">
-        <v>543</v>
+        <v>598</v>
       </c>
       <c r="Q103" t="s">
         <v>214</v>
@@ -7377,13 +7553,13 @@
     </row>
     <row r="104" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B104" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
       <c r="C104" t="s">
         <v>13</v>
       </c>
       <c r="D104" t="s">
-        <v>54</v>
+        <v>128</v>
       </c>
       <c r="E104">
         <v>0.21971250000000006</v>
@@ -7401,7 +7577,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J104" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K104">
         <v>1</v>
@@ -7413,10 +7589,10 @@
         <v>212</v>
       </c>
       <c r="O104" t="s">
-        <v>430</v>
+        <v>483</v>
       </c>
       <c r="P104" t="s">
-        <v>544</v>
+        <v>599</v>
       </c>
       <c r="Q104" t="s">
         <v>214</v>
@@ -7433,7 +7609,7 @@
     </row>
     <row r="105" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B105" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="C105" t="s">
         <v>13</v>
@@ -7457,7 +7633,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J105" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K105">
         <v>1</v>
@@ -7469,10 +7645,10 @@
         <v>212</v>
       </c>
       <c r="O105" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="P105" t="s">
-        <v>545</v>
+        <v>600</v>
       </c>
       <c r="Q105" t="s">
         <v>214</v>
@@ -7489,16 +7665,16 @@
     </row>
     <row r="106" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B106" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="C106" t="s">
         <v>13</v>
       </c>
       <c r="D106" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="E106">
-        <v>0.22680000000000003</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F106">
         <v>1365</v>
@@ -7513,7 +7689,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J106" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K106">
         <v>1</v>
@@ -7525,10 +7701,10 @@
         <v>212</v>
       </c>
       <c r="O106" t="s">
-        <v>432</v>
+        <v>485</v>
       </c>
       <c r="P106" t="s">
-        <v>546</v>
+        <v>601</v>
       </c>
       <c r="Q106" t="s">
         <v>214</v>
@@ -7545,7 +7721,7 @@
     </row>
     <row r="107" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B107" t="s">
-        <v>433</v>
+        <v>486</v>
       </c>
       <c r="C107" t="s">
         <v>13</v>
@@ -7554,7 +7730,7 @@
         <v>54</v>
       </c>
       <c r="E107">
-        <v>0.24451875000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F107">
         <v>1365</v>
@@ -7569,7 +7745,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J107" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K107">
         <v>1</v>
@@ -7581,10 +7757,10 @@
         <v>212</v>
       </c>
       <c r="O107" t="s">
-        <v>433</v>
+        <v>486</v>
       </c>
       <c r="P107" t="s">
-        <v>547</v>
+        <v>602</v>
       </c>
       <c r="Q107" t="s">
         <v>214</v>
@@ -7601,16 +7777,16 @@
     </row>
     <row r="108" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B108" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="C108" t="s">
         <v>13</v>
       </c>
       <c r="D108" t="s">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="E108">
-        <v>0.23388750000000003</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F108">
         <v>1365</v>
@@ -7625,7 +7801,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J108" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K108">
         <v>1</v>
@@ -7637,10 +7813,10 @@
         <v>212</v>
       </c>
       <c r="O108" t="s">
-        <v>434</v>
+        <v>487</v>
       </c>
       <c r="P108" t="s">
-        <v>548</v>
+        <v>603</v>
       </c>
       <c r="Q108" t="s">
         <v>214</v>
@@ -7657,16 +7833,16 @@
     </row>
     <row r="109" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B109" t="s">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="C109" t="s">
         <v>13</v>
       </c>
       <c r="D109" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="E109">
-        <v>0.23388750000000003</v>
+        <v>0.24451875000000001</v>
       </c>
       <c r="F109">
         <v>1365</v>
@@ -7681,7 +7857,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J109" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K109">
         <v>1</v>
@@ -7693,10 +7869,10 @@
         <v>212</v>
       </c>
       <c r="O109" t="s">
-        <v>435</v>
+        <v>488</v>
       </c>
       <c r="P109" t="s">
-        <v>549</v>
+        <v>604</v>
       </c>
       <c r="Q109" t="s">
         <v>214</v>
@@ -7713,7 +7889,7 @@
     </row>
     <row r="110" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B110" t="s">
-        <v>436</v>
+        <v>489</v>
       </c>
       <c r="C110" t="s">
         <v>13</v>
@@ -7737,7 +7913,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J110" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K110">
         <v>1</v>
@@ -7749,10 +7925,10 @@
         <v>212</v>
       </c>
       <c r="O110" t="s">
-        <v>436</v>
+        <v>489</v>
       </c>
       <c r="P110" t="s">
-        <v>550</v>
+        <v>605</v>
       </c>
       <c r="Q110" t="s">
         <v>214</v>
@@ -7769,13 +7945,13 @@
     </row>
     <row r="111" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B111" t="s">
-        <v>437</v>
+        <v>490</v>
       </c>
       <c r="C111" t="s">
         <v>13</v>
       </c>
       <c r="D111" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E111">
         <v>0.23388750000000003</v>
@@ -7793,7 +7969,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J111" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="K111">
         <v>1</v>
@@ -7805,10 +7981,10 @@
         <v>212</v>
       </c>
       <c r="O111" t="s">
-        <v>437</v>
+        <v>490</v>
       </c>
       <c r="P111" t="s">
-        <v>551</v>
+        <v>606</v>
       </c>
       <c r="Q111" t="s">
         <v>214</v>
@@ -7825,16 +8001,16 @@
     </row>
     <row r="112" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B112" t="s">
-        <v>438</v>
+        <v>491</v>
       </c>
       <c r="C112" t="s">
         <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E112">
-        <v>0.22680000000000003</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F112">
         <v>1365</v>
@@ -7849,7 +8025,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J112" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K112">
         <v>1</v>
@@ -7861,10 +8037,10 @@
         <v>212</v>
       </c>
       <c r="O112" t="s">
-        <v>438</v>
+        <v>491</v>
       </c>
       <c r="P112" t="s">
-        <v>552</v>
+        <v>607</v>
       </c>
       <c r="Q112" t="s">
         <v>214</v>
@@ -7881,7 +8057,7 @@
     </row>
     <row r="113" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B113" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="C113" t="s">
         <v>13</v>
@@ -7890,7 +8066,7 @@
         <v>139</v>
       </c>
       <c r="E113">
-        <v>0.22680000000000003</v>
+        <v>0.23388750000000003</v>
       </c>
       <c r="F113">
         <v>1365</v>
@@ -7905,7 +8081,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J113" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K113">
         <v>1</v>
@@ -7917,10 +8093,10 @@
         <v>212</v>
       </c>
       <c r="O113" t="s">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="P113" t="s">
-        <v>553</v>
+        <v>608</v>
       </c>
       <c r="Q113" t="s">
         <v>214</v>
@@ -7937,7 +8113,7 @@
     </row>
     <row r="114" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B114" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="C114" t="s">
         <v>13</v>
@@ -7961,7 +8137,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J114" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="K114">
         <v>1</v>
@@ -7973,10 +8149,10 @@
         <v>212</v>
       </c>
       <c r="O114" t="s">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="P114" t="s">
-        <v>554</v>
+        <v>609</v>
       </c>
       <c r="Q114" t="s">
         <v>214</v>
@@ -7993,7 +8169,7 @@
     </row>
     <row r="115" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B115" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="C115" t="s">
         <v>13</v>
@@ -8017,7 +8193,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J115" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="K115">
         <v>1</v>
@@ -8029,10 +8205,10 @@
         <v>212</v>
       </c>
       <c r="O115" t="s">
-        <v>441</v>
+        <v>494</v>
       </c>
       <c r="P115" t="s">
-        <v>555</v>
+        <v>610</v>
       </c>
       <c r="Q115" t="s">
         <v>214</v>
@@ -8049,13 +8225,13 @@
     </row>
     <row r="116" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B116" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="C116" t="s">
         <v>13</v>
       </c>
       <c r="D116" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E116">
         <v>0.22680000000000003</v>
@@ -8073,7 +8249,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J116" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="K116">
         <v>1</v>
@@ -8085,10 +8261,10 @@
         <v>212</v>
       </c>
       <c r="O116" t="s">
-        <v>442</v>
+        <v>495</v>
       </c>
       <c r="P116" t="s">
-        <v>556</v>
+        <v>611</v>
       </c>
       <c r="Q116" t="s">
         <v>214</v>
@@ -8105,13 +8281,13 @@
     </row>
     <row r="117" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B117" t="s">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="C117" t="s">
         <v>13</v>
       </c>
       <c r="D117" t="s">
-        <v>20</v>
+        <v>139</v>
       </c>
       <c r="E117">
         <v>0.22680000000000003</v>
@@ -8129,7 +8305,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J117" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="K117">
         <v>1</v>
@@ -8141,10 +8317,10 @@
         <v>212</v>
       </c>
       <c r="O117" t="s">
-        <v>443</v>
+        <v>496</v>
       </c>
       <c r="P117" t="s">
-        <v>557</v>
+        <v>612</v>
       </c>
       <c r="Q117" t="s">
         <v>214</v>
@@ -8161,7 +8337,7 @@
     </row>
     <row r="118" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B118" t="s">
-        <v>444</v>
+        <v>497</v>
       </c>
       <c r="C118" t="s">
         <v>13</v>
@@ -8185,7 +8361,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J118" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K118">
         <v>1</v>
@@ -8197,10 +8373,10 @@
         <v>212</v>
       </c>
       <c r="O118" t="s">
-        <v>444</v>
+        <v>497</v>
       </c>
       <c r="P118" t="s">
-        <v>558</v>
+        <v>613</v>
       </c>
       <c r="Q118" t="s">
         <v>214</v>
@@ -8217,7 +8393,7 @@
     </row>
     <row r="119" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B119" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
@@ -8241,7 +8417,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J119" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="K119">
         <v>1</v>
@@ -8253,10 +8429,10 @@
         <v>212</v>
       </c>
       <c r="O119" t="s">
-        <v>445</v>
+        <v>498</v>
       </c>
       <c r="P119" t="s">
-        <v>559</v>
+        <v>614</v>
       </c>
       <c r="Q119" t="s">
         <v>214</v>
@@ -8273,16 +8449,16 @@
     </row>
     <row r="120" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B120" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
       <c r="C120" t="s">
         <v>13</v>
       </c>
       <c r="D120" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E120">
-        <v>0.21971250000000006</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F120">
         <v>1365</v>
@@ -8297,7 +8473,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J120" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K120">
         <v>1</v>
@@ -8309,10 +8485,10 @@
         <v>212</v>
       </c>
       <c r="O120" t="s">
-        <v>446</v>
+        <v>499</v>
       </c>
       <c r="P120" t="s">
-        <v>560</v>
+        <v>615</v>
       </c>
       <c r="Q120" t="s">
         <v>214</v>
@@ -8329,16 +8505,16 @@
     </row>
     <row r="121" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B121" t="s">
-        <v>447</v>
+        <v>500</v>
       </c>
       <c r="C121" t="s">
         <v>13</v>
       </c>
       <c r="D121" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="E121">
-        <v>0.21971250000000006</v>
+        <v>0.22680000000000003</v>
       </c>
       <c r="F121">
         <v>1365</v>
@@ -8353,7 +8529,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J121" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K121">
         <v>1</v>
@@ -8365,10 +8541,10 @@
         <v>212</v>
       </c>
       <c r="O121" t="s">
-        <v>447</v>
+        <v>500</v>
       </c>
       <c r="P121" t="s">
-        <v>561</v>
+        <v>616</v>
       </c>
       <c r="Q121" t="s">
         <v>214</v>
@@ -8385,16 +8561,16 @@
     </row>
     <row r="122" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B122" t="s">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="C122" t="s">
         <v>13</v>
       </c>
       <c r="D122" t="s">
-        <v>100</v>
+        <v>47</v>
       </c>
       <c r="E122">
-        <v>0.25869375</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F122">
         <v>1365</v>
@@ -8409,7 +8585,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J122" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K122">
         <v>1</v>
@@ -8421,10 +8597,10 @@
         <v>212</v>
       </c>
       <c r="O122" t="s">
-        <v>448</v>
+        <v>501</v>
       </c>
       <c r="P122" t="s">
-        <v>562</v>
+        <v>617</v>
       </c>
       <c r="Q122" t="s">
         <v>214</v>
@@ -8441,16 +8617,16 @@
     </row>
     <row r="123" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B123" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="C123" t="s">
         <v>13</v>
       </c>
       <c r="D123" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E123">
-        <v>0.24451875000000001</v>
+        <v>0.21971250000000006</v>
       </c>
       <c r="F123">
         <v>1365</v>
@@ -8465,7 +8641,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J123" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K123">
         <v>1</v>
@@ -8477,10 +8653,10 @@
         <v>212</v>
       </c>
       <c r="O123" t="s">
-        <v>449</v>
+        <v>502</v>
       </c>
       <c r="P123" t="s">
-        <v>563</v>
+        <v>618</v>
       </c>
       <c r="Q123" t="s">
         <v>214</v>
@@ -8497,16 +8673,16 @@
     </row>
     <row r="124" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B124" t="s">
-        <v>450</v>
+        <v>503</v>
       </c>
       <c r="C124" t="s">
         <v>13</v>
       </c>
       <c r="D124" t="s">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="E124">
-        <v>0.21971250000000006</v>
+        <v>0.25869375</v>
       </c>
       <c r="F124">
         <v>1365</v>
@@ -8521,7 +8697,7 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J124" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="K124">
         <v>1</v>
@@ -8533,10 +8709,10 @@
         <v>212</v>
       </c>
       <c r="O124" t="s">
-        <v>450</v>
+        <v>503</v>
       </c>
       <c r="P124" t="s">
-        <v>546</v>
+        <v>619</v>
       </c>
       <c r="Q124" t="s">
         <v>214</v>
@@ -8553,16 +8729,16 @@
     </row>
     <row r="125" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B125" t="s">
-        <v>450</v>
+        <v>504</v>
       </c>
       <c r="C125" t="s">
         <v>13</v>
       </c>
       <c r="D125" t="s">
-        <v>153</v>
+        <v>54</v>
       </c>
       <c r="E125">
-        <v>0.21971250000000006</v>
+        <v>0.24451875000000001</v>
       </c>
       <c r="F125">
         <v>1365</v>
@@ -8577,13 +8753,90 @@
         <v>0.84455000000000002</v>
       </c>
       <c r="J125" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K125">
         <v>1</v>
       </c>
       <c r="L125">
         <v>20</v>
+      </c>
+      <c r="N125" t="s">
+        <v>212</v>
+      </c>
+      <c r="O125" t="s">
+        <v>504</v>
+      </c>
+      <c r="P125" t="s">
+        <v>620</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>214</v>
+      </c>
+      <c r="R125" t="s">
+        <v>215</v>
+      </c>
+      <c r="S125" t="s">
+        <v>216</v>
+      </c>
+      <c r="T125" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="126" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B126" t="s">
+        <v>505</v>
+      </c>
+      <c r="C126" t="s">
+        <v>13</v>
+      </c>
+      <c r="D126" t="s">
+        <v>153</v>
+      </c>
+      <c r="E126">
+        <v>0.21971250000000006</v>
+      </c>
+      <c r="F126">
+        <v>1365</v>
+      </c>
+      <c r="G126">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="H126">
+        <v>3.75</v>
+      </c>
+      <c r="I126">
+        <v>0.84455000000000002</v>
+      </c>
+      <c r="J126" t="s">
+        <v>152</v>
+      </c>
+      <c r="K126">
+        <v>1</v>
+      </c>
+      <c r="L126">
+        <v>20</v>
+      </c>
+      <c r="N126" t="s">
+        <v>212</v>
+      </c>
+      <c r="O126" t="s">
+        <v>505</v>
+      </c>
+      <c r="P126" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>214</v>
+      </c>
+      <c r="R126" t="s">
+        <v>215</v>
+      </c>
+      <c r="S126" t="s">
+        <v>216</v>
+      </c>
+      <c r="T126" t="s">
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -8592,7 +8845,1531 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13125183-6F1E-43D2-AD52-0031AE5A80D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB9B90C-346A-4661-899C-77B979CB63DE}">
+  <dimension ref="B9:T36"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F10" t="s">
+        <v>336</v>
+      </c>
+      <c r="G10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" t="s">
+        <v>7</v>
+      </c>
+      <c r="I10" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+      <c r="L10" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" t="s">
+        <v>206</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1</v>
+      </c>
+      <c r="P10" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>208</v>
+      </c>
+      <c r="R10" t="s">
+        <v>209</v>
+      </c>
+      <c r="S10" t="s">
+        <v>210</v>
+      </c>
+      <c r="T10" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B11" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" t="s">
+        <v>159</v>
+      </c>
+      <c r="D11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E11">
+        <v>2025</v>
+      </c>
+      <c r="F11">
+        <v>0.08</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>879.75</v>
+      </c>
+      <c r="I11">
+        <v>14.85</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>30</v>
+      </c>
+      <c r="L11">
+        <v>0.2337039712525093</v>
+      </c>
+      <c r="N11" t="s">
+        <v>212</v>
+      </c>
+      <c r="O11" t="s">
+        <v>337</v>
+      </c>
+      <c r="P11" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>214</v>
+      </c>
+      <c r="R11" t="s">
+        <v>215</v>
+      </c>
+      <c r="S11" t="s">
+        <v>334</v>
+      </c>
+      <c r="T11" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D12" t="s">
+        <v>340</v>
+      </c>
+      <c r="E12">
+        <v>2025</v>
+      </c>
+      <c r="F12">
+        <v>0.08</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>879.75</v>
+      </c>
+      <c r="I12">
+        <v>14.85</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>30</v>
+      </c>
+      <c r="L12">
+        <v>0.234255440085199</v>
+      </c>
+      <c r="N12" t="s">
+        <v>212</v>
+      </c>
+      <c r="O12" t="s">
+        <v>339</v>
+      </c>
+      <c r="P12" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>214</v>
+      </c>
+      <c r="R12" t="s">
+        <v>215</v>
+      </c>
+      <c r="S12" t="s">
+        <v>334</v>
+      </c>
+      <c r="T12" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B13" t="s">
+        <v>341</v>
+      </c>
+      <c r="C13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D13" t="s">
+        <v>342</v>
+      </c>
+      <c r="E13">
+        <v>2027</v>
+      </c>
+      <c r="F13">
+        <v>0.01</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1032.75</v>
+      </c>
+      <c r="I13">
+        <v>17.55</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>30</v>
+      </c>
+      <c r="L13">
+        <v>0.27003785896910409</v>
+      </c>
+      <c r="N13" t="s">
+        <v>212</v>
+      </c>
+      <c r="O13" t="s">
+        <v>341</v>
+      </c>
+      <c r="P13" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>214</v>
+      </c>
+      <c r="R13" t="s">
+        <v>215</v>
+      </c>
+      <c r="S13" t="s">
+        <v>334</v>
+      </c>
+      <c r="T13" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B14" t="s">
+        <v>343</v>
+      </c>
+      <c r="C14" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" t="s">
+        <v>178</v>
+      </c>
+      <c r="E14">
+        <v>2025</v>
+      </c>
+      <c r="F14">
+        <v>0.08</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>879.75</v>
+      </c>
+      <c r="I14">
+        <v>14.85</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>30</v>
+      </c>
+      <c r="L14">
+        <v>0.2665733883913311</v>
+      </c>
+      <c r="N14" t="s">
+        <v>212</v>
+      </c>
+      <c r="O14" t="s">
+        <v>343</v>
+      </c>
+      <c r="P14" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>214</v>
+      </c>
+      <c r="R14" t="s">
+        <v>215</v>
+      </c>
+      <c r="S14" t="s">
+        <v>334</v>
+      </c>
+      <c r="T14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B15" t="s">
+        <v>344</v>
+      </c>
+      <c r="C15" t="s">
+        <v>159</v>
+      </c>
+      <c r="D15" t="s">
+        <v>345</v>
+      </c>
+      <c r="E15">
+        <v>2026</v>
+      </c>
+      <c r="F15">
+        <v>0.12</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>879.75</v>
+      </c>
+      <c r="I15">
+        <v>14.85</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>30</v>
+      </c>
+      <c r="L15">
+        <v>0.2809344920019875</v>
+      </c>
+      <c r="N15" t="s">
+        <v>212</v>
+      </c>
+      <c r="O15" t="s">
+        <v>344</v>
+      </c>
+      <c r="P15" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>214</v>
+      </c>
+      <c r="R15" t="s">
+        <v>215</v>
+      </c>
+      <c r="S15" t="s">
+        <v>334</v>
+      </c>
+      <c r="T15" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B16" t="s">
+        <v>346</v>
+      </c>
+      <c r="C16" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" t="s">
+        <v>347</v>
+      </c>
+      <c r="E16">
+        <v>2025</v>
+      </c>
+      <c r="F16">
+        <v>1.2E-2</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1032.75</v>
+      </c>
+      <c r="I16">
+        <v>17.55</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>30</v>
+      </c>
+      <c r="L16">
+        <v>0.27842985990221908</v>
+      </c>
+      <c r="N16" t="s">
+        <v>212</v>
+      </c>
+      <c r="O16" t="s">
+        <v>346</v>
+      </c>
+      <c r="P16" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>214</v>
+      </c>
+      <c r="R16" t="s">
+        <v>215</v>
+      </c>
+      <c r="S16" t="s">
+        <v>334</v>
+      </c>
+      <c r="T16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B17" t="s">
+        <v>348</v>
+      </c>
+      <c r="C17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D17" t="s">
+        <v>200</v>
+      </c>
+      <c r="E17">
+        <v>2025</v>
+      </c>
+      <c r="F17">
+        <v>0.05</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1032.75</v>
+      </c>
+      <c r="I17">
+        <v>17.55</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>30</v>
+      </c>
+      <c r="L17">
+        <v>0.27361178776426898</v>
+      </c>
+      <c r="N17" t="s">
+        <v>212</v>
+      </c>
+      <c r="O17" t="s">
+        <v>348</v>
+      </c>
+      <c r="P17" t="s">
+        <v>372</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>214</v>
+      </c>
+      <c r="R17" t="s">
+        <v>215</v>
+      </c>
+      <c r="S17" t="s">
+        <v>334</v>
+      </c>
+      <c r="T17" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B18" t="s">
+        <v>349</v>
+      </c>
+      <c r="C18" t="s">
+        <v>159</v>
+      </c>
+      <c r="D18" t="s">
+        <v>178</v>
+      </c>
+      <c r="E18">
+        <v>2026</v>
+      </c>
+      <c r="F18">
+        <v>0.2</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>879.75</v>
+      </c>
+      <c r="I18">
+        <v>14.85</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>30</v>
+      </c>
+      <c r="L18">
+        <v>0.2665733883913311</v>
+      </c>
+      <c r="N18" t="s">
+        <v>212</v>
+      </c>
+      <c r="O18" t="s">
+        <v>349</v>
+      </c>
+      <c r="P18" t="s">
+        <v>373</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>214</v>
+      </c>
+      <c r="R18" t="s">
+        <v>215</v>
+      </c>
+      <c r="S18" t="s">
+        <v>334</v>
+      </c>
+      <c r="T18" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B19" t="s">
+        <v>350</v>
+      </c>
+      <c r="C19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19">
+        <v>2025</v>
+      </c>
+      <c r="F19">
+        <v>0.22</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>879.75</v>
+      </c>
+      <c r="I19">
+        <v>14.85</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>30</v>
+      </c>
+      <c r="L19">
+        <v>0.26045858769087071</v>
+      </c>
+      <c r="N19" t="s">
+        <v>212</v>
+      </c>
+      <c r="O19" t="s">
+        <v>350</v>
+      </c>
+      <c r="P19" t="s">
+        <v>374</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>214</v>
+      </c>
+      <c r="R19" t="s">
+        <v>215</v>
+      </c>
+      <c r="S19" t="s">
+        <v>334</v>
+      </c>
+      <c r="T19" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B20" t="s">
+        <v>351</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>352</v>
+      </c>
+      <c r="E20">
+        <v>2025</v>
+      </c>
+      <c r="F20">
+        <v>0.6</v>
+      </c>
+      <c r="G20">
+        <v>0.54</v>
+      </c>
+      <c r="H20">
+        <v>850</v>
+      </c>
+      <c r="I20">
+        <v>27</v>
+      </c>
+      <c r="J20">
+        <v>2.7</v>
+      </c>
+      <c r="K20">
+        <v>50</v>
+      </c>
+      <c r="N20" t="s">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s">
+        <v>351</v>
+      </c>
+      <c r="P20" t="s">
+        <v>375</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>214</v>
+      </c>
+      <c r="R20" t="s">
+        <v>215</v>
+      </c>
+      <c r="S20" t="s">
+        <v>216</v>
+      </c>
+      <c r="T20" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>352</v>
+      </c>
+      <c r="E21">
+        <v>2025</v>
+      </c>
+      <c r="F21">
+        <v>0.6</v>
+      </c>
+      <c r="G21">
+        <v>0.54</v>
+      </c>
+      <c r="H21">
+        <v>850</v>
+      </c>
+      <c r="I21">
+        <v>27</v>
+      </c>
+      <c r="J21">
+        <v>2.7</v>
+      </c>
+      <c r="K21">
+        <v>50</v>
+      </c>
+      <c r="N21" t="s">
+        <v>212</v>
+      </c>
+      <c r="O21" t="s">
+        <v>353</v>
+      </c>
+      <c r="P21" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>214</v>
+      </c>
+      <c r="R21" t="s">
+        <v>215</v>
+      </c>
+      <c r="S21" t="s">
+        <v>216</v>
+      </c>
+      <c r="T21" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B22" t="s">
+        <v>354</v>
+      </c>
+      <c r="C22" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E22">
+        <v>2025</v>
+      </c>
+      <c r="F22">
+        <v>0.1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>879.75</v>
+      </c>
+      <c r="I22">
+        <v>14.85</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>30</v>
+      </c>
+      <c r="L22">
+        <v>0.2305967012385047</v>
+      </c>
+      <c r="N22" t="s">
+        <v>212</v>
+      </c>
+      <c r="O22" t="s">
+        <v>354</v>
+      </c>
+      <c r="P22" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>214</v>
+      </c>
+      <c r="R22" t="s">
+        <v>215</v>
+      </c>
+      <c r="S22" t="s">
+        <v>334</v>
+      </c>
+      <c r="T22" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B23" t="s">
+        <v>355</v>
+      </c>
+      <c r="C23" t="s">
+        <v>159</v>
+      </c>
+      <c r="D23" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23">
+        <v>2025</v>
+      </c>
+      <c r="F23">
+        <v>0.23</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>879.75</v>
+      </c>
+      <c r="I23">
+        <v>14.85</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>30</v>
+      </c>
+      <c r="L23">
+        <v>0.25377378855731381</v>
+      </c>
+      <c r="N23" t="s">
+        <v>212</v>
+      </c>
+      <c r="O23" t="s">
+        <v>355</v>
+      </c>
+      <c r="P23" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>214</v>
+      </c>
+      <c r="R23" t="s">
+        <v>215</v>
+      </c>
+      <c r="S23" t="s">
+        <v>334</v>
+      </c>
+      <c r="T23" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>178</v>
+      </c>
+      <c r="E24">
+        <v>2025</v>
+      </c>
+      <c r="F24">
+        <v>0.13</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>879.75</v>
+      </c>
+      <c r="I24">
+        <v>14.85</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>30</v>
+      </c>
+      <c r="L24">
+        <v>0.2665733883913311</v>
+      </c>
+      <c r="N24" t="s">
+        <v>212</v>
+      </c>
+      <c r="O24" t="s">
+        <v>357</v>
+      </c>
+      <c r="P24" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>214</v>
+      </c>
+      <c r="R24" t="s">
+        <v>215</v>
+      </c>
+      <c r="S24" t="s">
+        <v>334</v>
+      </c>
+      <c r="T24" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" t="s">
+        <v>159</v>
+      </c>
+      <c r="D25" t="s">
+        <v>182</v>
+      </c>
+      <c r="E25">
+        <v>2028</v>
+      </c>
+      <c r="F25">
+        <v>0.08</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>879.75</v>
+      </c>
+      <c r="I25">
+        <v>14.85</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>30</v>
+      </c>
+      <c r="L25">
+        <v>0.27322070445839058</v>
+      </c>
+      <c r="N25" t="s">
+        <v>212</v>
+      </c>
+      <c r="O25" t="s">
+        <v>358</v>
+      </c>
+      <c r="P25" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>214</v>
+      </c>
+      <c r="R25" t="s">
+        <v>215</v>
+      </c>
+      <c r="S25" t="s">
+        <v>334</v>
+      </c>
+      <c r="T25" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B26" t="s">
+        <v>359</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" t="s">
+        <v>360</v>
+      </c>
+      <c r="E26">
+        <v>2025</v>
+      </c>
+      <c r="F26">
+        <v>0.08</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>879.75</v>
+      </c>
+      <c r="I26">
+        <v>14.85</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>30</v>
+      </c>
+      <c r="L26">
+        <v>0.28108022139742972</v>
+      </c>
+      <c r="N26" t="s">
+        <v>212</v>
+      </c>
+      <c r="O26" t="s">
+        <v>359</v>
+      </c>
+      <c r="P26" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>214</v>
+      </c>
+      <c r="R26" t="s">
+        <v>215</v>
+      </c>
+      <c r="S26" t="s">
+        <v>334</v>
+      </c>
+      <c r="T26" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B27" t="s">
+        <v>361</v>
+      </c>
+      <c r="C27" t="s">
+        <v>159</v>
+      </c>
+      <c r="D27" t="s">
+        <v>345</v>
+      </c>
+      <c r="E27">
+        <v>2025</v>
+      </c>
+      <c r="F27">
+        <v>0.05</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27">
+        <v>1032.75</v>
+      </c>
+      <c r="I27">
+        <v>17.55</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>30</v>
+      </c>
+      <c r="L27">
+        <v>0.2809344920019875</v>
+      </c>
+      <c r="N27" t="s">
+        <v>212</v>
+      </c>
+      <c r="O27" t="s">
+        <v>361</v>
+      </c>
+      <c r="P27" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>214</v>
+      </c>
+      <c r="R27" t="s">
+        <v>215</v>
+      </c>
+      <c r="S27" t="s">
+        <v>334</v>
+      </c>
+      <c r="T27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B28" t="s">
+        <v>362</v>
+      </c>
+      <c r="C28" t="s">
+        <v>159</v>
+      </c>
+      <c r="D28" t="s">
+        <v>356</v>
+      </c>
+      <c r="E28">
+        <v>2025</v>
+      </c>
+      <c r="F28">
+        <v>0.2</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>879.75</v>
+      </c>
+      <c r="I28">
+        <v>14.85</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>30</v>
+      </c>
+      <c r="L28">
+        <v>0.25377378855731381</v>
+      </c>
+      <c r="N28" t="s">
+        <v>212</v>
+      </c>
+      <c r="O28" t="s">
+        <v>362</v>
+      </c>
+      <c r="P28" t="s">
+        <v>378</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>214</v>
+      </c>
+      <c r="R28" t="s">
+        <v>215</v>
+      </c>
+      <c r="S28" t="s">
+        <v>334</v>
+      </c>
+      <c r="T28" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B29" t="s">
+        <v>363</v>
+      </c>
+      <c r="C29" t="s">
+        <v>159</v>
+      </c>
+      <c r="D29" t="s">
+        <v>170</v>
+      </c>
+      <c r="E29">
+        <v>2025</v>
+      </c>
+      <c r="F29">
+        <v>0.2</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>879.75</v>
+      </c>
+      <c r="I29">
+        <v>14.85</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>30</v>
+      </c>
+      <c r="L29">
+        <v>0.26529691102798381</v>
+      </c>
+      <c r="N29" t="s">
+        <v>212</v>
+      </c>
+      <c r="O29" t="s">
+        <v>363</v>
+      </c>
+      <c r="P29" t="s">
+        <v>379</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>214</v>
+      </c>
+      <c r="R29" t="s">
+        <v>215</v>
+      </c>
+      <c r="S29" t="s">
+        <v>334</v>
+      </c>
+      <c r="T29" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B30" t="s">
+        <v>364</v>
+      </c>
+      <c r="C30" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" t="s">
+        <v>365</v>
+      </c>
+      <c r="E30">
+        <v>2025</v>
+      </c>
+      <c r="F30">
+        <v>0.22</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30">
+        <v>879.75</v>
+      </c>
+      <c r="I30">
+        <v>14.85</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>30</v>
+      </c>
+      <c r="L30">
+        <v>0.24039908464852369</v>
+      </c>
+      <c r="N30" t="s">
+        <v>212</v>
+      </c>
+      <c r="O30" t="s">
+        <v>364</v>
+      </c>
+      <c r="P30" t="s">
+        <v>380</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>214</v>
+      </c>
+      <c r="R30" t="s">
+        <v>215</v>
+      </c>
+      <c r="S30" t="s">
+        <v>334</v>
+      </c>
+      <c r="T30" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D31" t="s">
+        <v>340</v>
+      </c>
+      <c r="E31">
+        <v>2025</v>
+      </c>
+      <c r="F31">
+        <v>0.22</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>879.75</v>
+      </c>
+      <c r="I31">
+        <v>14.85</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>30</v>
+      </c>
+      <c r="L31">
+        <v>0.23425544008519902</v>
+      </c>
+      <c r="N31" t="s">
+        <v>212</v>
+      </c>
+      <c r="O31" t="s">
+        <v>366</v>
+      </c>
+      <c r="P31" t="s">
+        <v>381</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>214</v>
+      </c>
+      <c r="R31" t="s">
+        <v>215</v>
+      </c>
+      <c r="S31" t="s">
+        <v>334</v>
+      </c>
+      <c r="T31" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B32" t="s">
+        <v>367</v>
+      </c>
+      <c r="C32" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" t="s">
+        <v>174</v>
+      </c>
+      <c r="E32">
+        <v>2025</v>
+      </c>
+      <c r="F32">
+        <v>0.2</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>879.75</v>
+      </c>
+      <c r="I32">
+        <v>14.85</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>30</v>
+      </c>
+      <c r="L32">
+        <v>0.26045858769087071</v>
+      </c>
+      <c r="N32" t="s">
+        <v>212</v>
+      </c>
+      <c r="O32" t="s">
+        <v>367</v>
+      </c>
+      <c r="P32" t="s">
+        <v>382</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>214</v>
+      </c>
+      <c r="R32" t="s">
+        <v>215</v>
+      </c>
+      <c r="S32" t="s">
+        <v>334</v>
+      </c>
+      <c r="T32" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B33" t="s">
+        <v>368</v>
+      </c>
+      <c r="C33" t="s">
+        <v>159</v>
+      </c>
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33">
+        <v>2025</v>
+      </c>
+      <c r="F33">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="G33">
+        <v>1</v>
+      </c>
+      <c r="H33">
+        <v>765</v>
+      </c>
+      <c r="I33">
+        <v>13.5</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>30</v>
+      </c>
+      <c r="L33">
+        <v>0.26529691102798381</v>
+      </c>
+      <c r="N33" t="s">
+        <v>212</v>
+      </c>
+      <c r="O33" t="s">
+        <v>368</v>
+      </c>
+      <c r="P33" t="s">
+        <v>383</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>214</v>
+      </c>
+      <c r="R33" t="s">
+        <v>215</v>
+      </c>
+      <c r="S33" t="s">
+        <v>334</v>
+      </c>
+      <c r="T33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B34" t="s">
+        <v>369</v>
+      </c>
+      <c r="C34" t="s">
+        <v>159</v>
+      </c>
+      <c r="D34" t="s">
+        <v>170</v>
+      </c>
+      <c r="E34">
+        <v>2025</v>
+      </c>
+      <c r="F34">
+        <v>0.3</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34">
+        <v>879.75</v>
+      </c>
+      <c r="I34">
+        <v>14.85</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>30</v>
+      </c>
+      <c r="L34">
+        <v>0.26529691102798381</v>
+      </c>
+      <c r="N34" t="s">
+        <v>212</v>
+      </c>
+      <c r="O34" t="s">
+        <v>369</v>
+      </c>
+      <c r="P34" t="s">
+        <v>384</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>214</v>
+      </c>
+      <c r="R34" t="s">
+        <v>215</v>
+      </c>
+      <c r="S34" t="s">
+        <v>334</v>
+      </c>
+      <c r="T34" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B35" t="s">
+        <v>370</v>
+      </c>
+      <c r="C35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35">
+        <v>2026</v>
+      </c>
+      <c r="F35">
+        <v>0.3</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35">
+        <v>879.75</v>
+      </c>
+      <c r="I35">
+        <v>14.85</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>30</v>
+      </c>
+      <c r="L35">
+        <v>0.2665733883913311</v>
+      </c>
+      <c r="N35" t="s">
+        <v>212</v>
+      </c>
+      <c r="O35" t="s">
+        <v>370</v>
+      </c>
+      <c r="P35" t="s">
+        <v>385</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>214</v>
+      </c>
+      <c r="R35" t="s">
+        <v>215</v>
+      </c>
+      <c r="S35" t="s">
+        <v>334</v>
+      </c>
+      <c r="T35" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="B36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" t="s">
+        <v>178</v>
+      </c>
+      <c r="E36">
+        <v>2025</v>
+      </c>
+      <c r="F36">
+        <v>0.25</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36">
+        <v>879.75</v>
+      </c>
+      <c r="I36">
+        <v>14.85</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>30</v>
+      </c>
+      <c r="L36">
+        <v>0.2665733883913311</v>
+      </c>
+      <c r="N36" t="s">
+        <v>212</v>
+      </c>
+      <c r="O36" t="s">
+        <v>371</v>
+      </c>
+      <c r="P36" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>214</v>
+      </c>
+      <c r="R36" t="s">
+        <v>215</v>
+      </c>
+      <c r="S36" t="s">
+        <v>334</v>
+      </c>
+      <c r="T36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C46B5DFC-5B24-433F-B80E-C4E79D4316E2}">
   <dimension ref="B9:T160"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14687,7 +16464,7 @@
         <v>152</v>
       </c>
       <c r="P124" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q124" t="s">
         <v>214</v>
@@ -14740,7 +16517,7 @@
         <v>154</v>
       </c>
       <c r="P125" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q125" t="s">
         <v>214</v>
@@ -14793,7 +16570,7 @@
         <v>157</v>
       </c>
       <c r="P126" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q126" t="s">
         <v>214</v>
@@ -14846,7 +16623,7 @@
         <v>158</v>
       </c>
       <c r="P127" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q127" t="s">
         <v>214</v>
@@ -14855,7 +16632,7 @@
         <v>215</v>
       </c>
       <c r="S127" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T127" t="s">
         <v>313</v>
@@ -14872,10 +16649,10 @@
         <v>160</v>
       </c>
       <c r="E128">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F128">
-        <v>3.5999999999999999E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G128">
         <v>1</v>
@@ -14890,10 +16667,10 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L128">
-        <v>0.26330420504991281</v>
+        <v>0.24629169837206899</v>
       </c>
       <c r="N128" t="s">
         <v>212</v>
@@ -14902,7 +16679,7 @@
         <v>161</v>
       </c>
       <c r="P128" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q128" t="s">
         <v>214</v>
@@ -14911,7 +16688,7 @@
         <v>215</v>
       </c>
       <c r="S128" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T128" t="s">
         <v>313</v>
@@ -14919,19 +16696,19 @@
     </row>
     <row r="129" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B129" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C129" t="s">
         <v>159</v>
       </c>
       <c r="D129" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E129">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F129">
-        <v>0.02</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G129">
         <v>1</v>
@@ -14946,10 +16723,10 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L129">
-        <v>0.26330420504991281</v>
+        <v>0.24078085835754717</v>
       </c>
       <c r="N129" t="s">
         <v>212</v>
@@ -14958,7 +16735,7 @@
         <v>163</v>
       </c>
       <c r="P129" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q129" t="s">
         <v>214</v>
@@ -14967,7 +16744,7 @@
         <v>215</v>
       </c>
       <c r="S129" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T129" t="s">
         <v>313</v>
@@ -14975,19 +16752,19 @@
     </row>
     <row r="130" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B130" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C130" t="s">
         <v>159</v>
       </c>
       <c r="D130" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E130">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F130">
-        <v>0.03</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="G130">
         <v>1</v>
@@ -15002,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L130">
-        <v>0.26251514105821983</v>
+        <v>0.26453653240290731</v>
       </c>
       <c r="N130" t="s">
         <v>212</v>
@@ -15014,7 +16791,7 @@
         <v>165</v>
       </c>
       <c r="P130" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q130" t="s">
         <v>214</v>
@@ -15023,7 +16800,7 @@
         <v>215</v>
       </c>
       <c r="S130" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T130" t="s">
         <v>313</v>
@@ -15043,7 +16820,7 @@
         <v>2016</v>
       </c>
       <c r="F131">
-        <v>1.2E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G131">
         <v>1</v>
@@ -15061,7 +16838,7 @@
         <v>39</v>
       </c>
       <c r="L131">
-        <v>0.24629169837206899</v>
+        <v>0.26453653240290731</v>
       </c>
       <c r="N131" t="s">
         <v>212</v>
@@ -15070,7 +16847,7 @@
         <v>167</v>
       </c>
       <c r="P131" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q131" t="s">
         <v>214</v>
@@ -15079,7 +16856,7 @@
         <v>215</v>
       </c>
       <c r="S131" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T131" t="s">
         <v>313</v>
@@ -15096,10 +16873,10 @@
         <v>166</v>
       </c>
       <c r="E132">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F132">
-        <v>1.5E-3</v>
+        <v>0.03</v>
       </c>
       <c r="G132">
         <v>1</v>
@@ -15114,10 +16891,10 @@
         <v>0</v>
       </c>
       <c r="K132">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L132">
-        <v>0.24078085835754717</v>
+        <v>0.26251514105821983</v>
       </c>
       <c r="N132" t="s">
         <v>212</v>
@@ -15126,7 +16903,7 @@
         <v>169</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q132" t="s">
         <v>214</v>
@@ -15135,7 +16912,7 @@
         <v>215</v>
       </c>
       <c r="S132" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T132" t="s">
         <v>313</v>
@@ -15182,7 +16959,7 @@
         <v>171</v>
       </c>
       <c r="P133" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q133" t="s">
         <v>214</v>
@@ -15191,7 +16968,7 @@
         <v>215</v>
       </c>
       <c r="S133" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T133" t="s">
         <v>313</v>
@@ -15208,28 +16985,28 @@
         <v>170</v>
       </c>
       <c r="E134">
-        <v>2025</v>
+        <v>2016</v>
       </c>
       <c r="F134">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="G134">
         <v>1</v>
       </c>
       <c r="H134">
-        <v>879.75</v>
+        <v>1032.75</v>
       </c>
       <c r="I134">
-        <v>14.85</v>
+        <v>17.55</v>
       </c>
       <c r="J134">
         <v>0</v>
       </c>
       <c r="K134">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L134">
-        <v>0.26045858769087071</v>
+        <v>0.26529691102798381</v>
       </c>
       <c r="N134" t="s">
         <v>212</v>
@@ -15247,7 +17024,7 @@
         <v>215</v>
       </c>
       <c r="S134" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T134" t="s">
         <v>313</v>
@@ -15255,19 +17032,19 @@
     </row>
     <row r="135" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B135" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C135" t="s">
         <v>159</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E135">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F135">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G135">
         <v>1</v>
@@ -15282,7 +17059,7 @@
         <v>0</v>
       </c>
       <c r="K135">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L135">
         <v>0.26529691102798381</v>
@@ -15303,7 +17080,7 @@
         <v>215</v>
       </c>
       <c r="S135" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T135" t="s">
         <v>313</v>
@@ -15320,10 +17097,10 @@
         <v>172</v>
       </c>
       <c r="E136">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F136">
-        <v>0.04</v>
+        <v>0.02</v>
       </c>
       <c r="G136">
         <v>1</v>
@@ -15338,19 +17115,19 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L136">
-        <v>0.26529691102798381</v>
+        <v>0.26329199375122608</v>
       </c>
       <c r="N136" t="s">
         <v>212</v>
       </c>
       <c r="O136" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="P136" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q136" t="s">
         <v>214</v>
@@ -15359,7 +17136,7 @@
         <v>215</v>
       </c>
       <c r="S136" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T136" t="s">
         <v>313</v>
@@ -15367,19 +17144,19 @@
     </row>
     <row r="137" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B137" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C137" t="s">
         <v>159</v>
       </c>
       <c r="D137" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E137">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F137">
-        <v>0.02</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G137">
         <v>1</v>
@@ -15394,7 +17171,7 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L137">
         <v>0.26329199375122608</v>
@@ -15403,10 +17180,10 @@
         <v>212</v>
       </c>
       <c r="O137" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="P137" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q137" t="s">
         <v>214</v>
@@ -15415,7 +17192,7 @@
         <v>215</v>
       </c>
       <c r="S137" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T137" t="s">
         <v>313</v>
@@ -15432,37 +17209,37 @@
         <v>174</v>
       </c>
       <c r="E138">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="F138">
-        <v>5.2999999999999999E-2</v>
+        <v>0.08</v>
       </c>
       <c r="G138">
         <v>1</v>
       </c>
       <c r="H138">
-        <v>1032.75</v>
+        <v>879.75</v>
       </c>
       <c r="I138">
-        <v>17.55</v>
+        <v>14.85</v>
       </c>
       <c r="J138">
         <v>0</v>
       </c>
       <c r="K138">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L138">
-        <v>0.26329199375122608</v>
+        <v>0.26045858769087071</v>
       </c>
       <c r="N138" t="s">
         <v>212</v>
       </c>
       <c r="O138" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="P138" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q138" t="s">
         <v>214</v>
@@ -15471,7 +17248,7 @@
         <v>215</v>
       </c>
       <c r="S138" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T138" t="s">
         <v>313</v>
@@ -15488,10 +17265,10 @@
         <v>176</v>
       </c>
       <c r="E139">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="F139">
-        <v>5.3E-3</v>
+        <v>0.01</v>
       </c>
       <c r="G139">
         <v>1</v>
@@ -15506,19 +17283,19 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L139">
-        <v>0.27322070445839058</v>
+        <v>0.26631149817827809</v>
       </c>
       <c r="N139" t="s">
         <v>212</v>
       </c>
       <c r="O139" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P139" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q139" t="s">
         <v>214</v>
@@ -15527,7 +17304,7 @@
         <v>215</v>
       </c>
       <c r="S139" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T139" t="s">
         <v>313</v>
@@ -15535,19 +17312,19 @@
     </row>
     <row r="140" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B140" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C140" t="s">
         <v>159</v>
       </c>
       <c r="D140" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E140">
-        <v>2017</v>
+        <v>2028</v>
       </c>
       <c r="F140">
-        <v>1.2E-2</v>
+        <v>0.01</v>
       </c>
       <c r="G140">
         <v>1</v>
@@ -15562,19 +17339,19 @@
         <v>0</v>
       </c>
       <c r="K140">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L140">
-        <v>0.27498020929905181</v>
+        <v>0.26631149817827809</v>
       </c>
       <c r="N140" t="s">
         <v>212</v>
       </c>
       <c r="O140" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="P140" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q140" t="s">
         <v>214</v>
@@ -15583,7 +17360,7 @@
         <v>215</v>
       </c>
       <c r="S140" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T140" t="s">
         <v>313</v>
@@ -15591,19 +17368,19 @@
     </row>
     <row r="141" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B141" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C141" t="s">
         <v>159</v>
       </c>
       <c r="D141" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E141">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="F141">
-        <v>2.3E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="G141">
         <v>1</v>
@@ -15618,19 +17395,19 @@
         <v>0</v>
       </c>
       <c r="K141">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L141">
-        <v>0.274332077855444</v>
+        <v>0.2665733883913311</v>
       </c>
       <c r="N141" t="s">
         <v>212</v>
       </c>
       <c r="O141" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="P141" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q141" t="s">
         <v>214</v>
@@ -15639,7 +17416,7 @@
         <v>215</v>
       </c>
       <c r="S141" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T141" t="s">
         <v>313</v>
@@ -15647,19 +17424,19 @@
     </row>
     <row r="142" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B142" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C142" t="s">
         <v>159</v>
       </c>
       <c r="D142" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E142">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F142">
-        <v>9.4000000000000004E-3</v>
+        <v>2.3E-2</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -15674,16 +17451,16 @@
         <v>0</v>
       </c>
       <c r="K142">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L142">
-        <v>0.28021747724695228</v>
+        <v>0.274332077855444</v>
       </c>
       <c r="N142" t="s">
         <v>212</v>
       </c>
       <c r="O142" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="P142" t="s">
         <v>312</v>
@@ -15695,7 +17472,7 @@
         <v>215</v>
       </c>
       <c r="S142" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T142" t="s">
         <v>313</v>
@@ -15712,10 +17489,10 @@
         <v>182</v>
       </c>
       <c r="E143">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="F143">
-        <v>7.9000000000000008E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="G143">
         <v>1</v>
@@ -15730,19 +17507,19 @@
         <v>0</v>
       </c>
       <c r="K143">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L143">
-        <v>0.28021747724695228</v>
+        <v>0.27322070445839058</v>
       </c>
       <c r="N143" t="s">
         <v>212</v>
       </c>
       <c r="O143" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="P143" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q143" t="s">
         <v>214</v>
@@ -15751,7 +17528,7 @@
         <v>215</v>
       </c>
       <c r="S143" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T143" t="s">
         <v>313</v>
@@ -15768,10 +17545,10 @@
         <v>184</v>
       </c>
       <c r="E144">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F144">
-        <v>0.02</v>
+        <v>1.7500000000000002E-2</v>
       </c>
       <c r="G144">
         <v>1</v>
@@ -15786,19 +17563,19 @@
         <v>0</v>
       </c>
       <c r="K144">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L144">
-        <v>0.277732756009617</v>
+        <v>0.27719217365775212</v>
       </c>
       <c r="N144" t="s">
         <v>212</v>
       </c>
       <c r="O144" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q144" t="s">
         <v>214</v>
@@ -15807,7 +17584,7 @@
         <v>215</v>
       </c>
       <c r="S144" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T144" t="s">
         <v>313</v>
@@ -15815,46 +17592,46 @@
     </row>
     <row r="145" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B145" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C145" t="s">
         <v>159</v>
       </c>
       <c r="D145" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E145">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="F145">
-        <v>5.2999999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="G145">
         <v>1</v>
       </c>
       <c r="H145">
-        <v>879.75</v>
+        <v>1032.75</v>
       </c>
       <c r="I145">
-        <v>14.85</v>
+        <v>17.55</v>
       </c>
       <c r="J145">
         <v>0</v>
       </c>
       <c r="K145">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L145">
-        <v>0.277732756009617</v>
+        <v>0.2795030935713137</v>
       </c>
       <c r="N145" t="s">
         <v>212</v>
       </c>
       <c r="O145" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="P145" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q145" t="s">
         <v>214</v>
@@ -15863,7 +17640,7 @@
         <v>215</v>
       </c>
       <c r="S145" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T145" t="s">
         <v>313</v>
@@ -15871,46 +17648,46 @@
     </row>
     <row r="146" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B146" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C146" t="s">
         <v>159</v>
       </c>
       <c r="D146" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E146">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="F146">
-        <v>2.1100000000000001E-2</v>
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="G146">
         <v>1</v>
       </c>
       <c r="H146">
-        <v>1032.75</v>
+        <v>879.75</v>
       </c>
       <c r="I146">
-        <v>17.55</v>
+        <v>14.85</v>
       </c>
       <c r="J146">
         <v>0</v>
       </c>
       <c r="K146">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L146">
-        <v>0.27773275600961694</v>
+        <v>0.2795030935713137</v>
       </c>
       <c r="N146" t="s">
         <v>212</v>
       </c>
       <c r="O146" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="P146" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q146" t="s">
         <v>214</v>
@@ -15919,7 +17696,7 @@
         <v>215</v>
       </c>
       <c r="S146" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T146" t="s">
         <v>313</v>
@@ -15936,10 +17713,10 @@
         <v>186</v>
       </c>
       <c r="E147">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="F147">
-        <v>2.5000000000000001E-3</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G147">
         <v>1</v>
@@ -15954,19 +17731,19 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L147">
-        <v>0.27901554374351129</v>
+        <v>0.2795030935713137</v>
       </c>
       <c r="N147" t="s">
         <v>212</v>
       </c>
       <c r="O147" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="P147" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q147" t="s">
         <v>214</v>
@@ -15975,7 +17752,7 @@
         <v>215</v>
       </c>
       <c r="S147" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T147" t="s">
         <v>313</v>
@@ -15983,19 +17760,19 @@
     </row>
     <row r="148" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B148" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C148" t="s">
         <v>159</v>
       </c>
       <c r="D148" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E148">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F148">
-        <v>5.0000000000000001E-3</v>
+        <v>7.9000000000000008E-3</v>
       </c>
       <c r="G148">
         <v>1</v>
@@ -16010,19 +17787,19 @@
         <v>0</v>
       </c>
       <c r="K148">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L148">
-        <v>0.28521940119989581</v>
+        <v>0.2795030935713137</v>
       </c>
       <c r="N148" t="s">
         <v>212</v>
       </c>
       <c r="O148" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="P148" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q148" t="s">
         <v>214</v>
@@ -16031,7 +17808,7 @@
         <v>215</v>
       </c>
       <c r="S148" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T148" t="s">
         <v>313</v>
@@ -16048,10 +17825,10 @@
         <v>188</v>
       </c>
       <c r="E149">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F149">
-        <v>3.2000000000000002E-3</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="G149">
         <v>1</v>
@@ -16066,19 +17843,19 @@
         <v>0</v>
       </c>
       <c r="K149">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L149">
-        <v>0.28521940119989581</v>
+        <v>0.28178245365487259</v>
       </c>
       <c r="N149" t="s">
         <v>212</v>
       </c>
       <c r="O149" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="P149" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="Q149" t="s">
         <v>214</v>
@@ -16087,7 +17864,7 @@
         <v>215</v>
       </c>
       <c r="S149" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T149" t="s">
         <v>313</v>
@@ -16095,19 +17872,19 @@
     </row>
     <row r="150" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B150" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C150" t="s">
         <v>159</v>
       </c>
       <c r="D150" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E150">
-        <v>2018</v>
+        <v>2028</v>
       </c>
       <c r="F150">
-        <v>1.2999999999999999E-2</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="G150">
         <v>1</v>
@@ -16122,27 +17899,48 @@
         <v>0</v>
       </c>
       <c r="K150">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L150">
-        <v>0.28664197561383281</v>
+        <v>0.28178245365487259</v>
+      </c>
+      <c r="N150" t="s">
+        <v>212</v>
+      </c>
+      <c r="O150" t="s">
+        <v>201</v>
+      </c>
+      <c r="P150" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>214</v>
+      </c>
+      <c r="R150" t="s">
+        <v>215</v>
+      </c>
+      <c r="S150" t="s">
+        <v>334</v>
+      </c>
+      <c r="T150" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="151" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B151" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C151" t="s">
         <v>159</v>
       </c>
       <c r="D151" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E151">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F151">
-        <v>4.4999999999999997E-3</v>
+        <v>3.5999999999999999E-3</v>
       </c>
       <c r="G151">
         <v>1</v>
@@ -16157,10 +17955,31 @@
         <v>0</v>
       </c>
       <c r="K151">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="L151">
-        <v>0.28877962223260251</v>
+        <v>0.27735611326358628</v>
+      </c>
+      <c r="N151" t="s">
+        <v>212</v>
+      </c>
+      <c r="O151" t="s">
+        <v>202</v>
+      </c>
+      <c r="P151" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>214</v>
+      </c>
+      <c r="R151" t="s">
+        <v>215</v>
+      </c>
+      <c r="S151" t="s">
+        <v>334</v>
+      </c>
+      <c r="T151" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="152" spans="2:20" x14ac:dyDescent="0.45">
@@ -16174,10 +17993,10 @@
         <v>192</v>
       </c>
       <c r="E152">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="F152">
-        <v>5.3E-3</v>
+        <v>4.4999999999999997E-3</v>
       </c>
       <c r="G152">
         <v>1</v>
@@ -16192,27 +18011,27 @@
         <v>0</v>
       </c>
       <c r="K152">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L152">
-        <v>0.28877962223260251</v>
+        <v>0.28998156286768029</v>
       </c>
     </row>
     <row r="153" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B153" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C153" t="s">
         <v>159</v>
       </c>
       <c r="D153" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E153">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F153">
-        <v>8.9999999999999993E-3</v>
+        <v>5.3E-3</v>
       </c>
       <c r="G153">
         <v>1</v>
@@ -16227,10 +18046,10 @@
         <v>0</v>
       </c>
       <c r="K153">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L153">
-        <v>0.28178245365487259</v>
+        <v>0.28998156286768029</v>
       </c>
     </row>
     <row r="154" spans="2:20" x14ac:dyDescent="0.45">
@@ -16244,10 +18063,10 @@
         <v>194</v>
       </c>
       <c r="E154">
-        <v>2028</v>
+        <v>2021</v>
       </c>
       <c r="F154">
-        <v>1.0999999999999999E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="G154">
         <v>1</v>
@@ -16262,27 +18081,27 @@
         <v>0</v>
       </c>
       <c r="K154">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L154">
-        <v>0.28178245365487259</v>
+        <v>0.2859784327483052</v>
       </c>
     </row>
     <row r="155" spans="2:20" x14ac:dyDescent="0.45">
       <c r="B155" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C155" t="s">
         <v>159</v>
       </c>
       <c r="D155" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E155">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="F155">
-        <v>0.01</v>
+        <v>3.2000000000000002E-3</v>
       </c>
       <c r="G155">
         <v>1</v>
@@ -16297,10 +18116,10 @@
         <v>0</v>
       </c>
       <c r="K155">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="L155">
-        <v>0.26631149817827809</v>
+        <v>0.2859784327483052</v>
       </c>
     </row>
     <row r="156" spans="2:20" x14ac:dyDescent="0.45">
@@ -16314,10 +18133,10 @@
         <v>196</v>
       </c>
       <c r="E156">
-        <v>2028</v>
+        <v>2018</v>
       </c>
       <c r="F156">
-        <v>0.01</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="G156">
         <v>1</v>
@@ -16332,10 +18151,10 @@
         <v>0</v>
       </c>
       <c r="K156">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L156">
-        <v>0.26631149817827809</v>
+        <v>0.28628213571803879</v>
       </c>
     </row>
     <row r="157" spans="2:20" x14ac:dyDescent="0.45">
@@ -16349,10 +18168,10 @@
         <v>198</v>
       </c>
       <c r="E157">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="F157">
-        <v>3.2399999999999998E-2</v>
+        <v>2.5000000000000001E-3</v>
       </c>
       <c r="G157">
         <v>1</v>
@@ -16367,10 +18186,10 @@
         <v>0</v>
       </c>
       <c r="K157">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="L157">
-        <v>0.2665733883913311</v>
+        <v>0.2790089477808862</v>
       </c>
     </row>
     <row r="158" spans="2:20" x14ac:dyDescent="0.45">
@@ -16384,10 +18203,10 @@
         <v>200</v>
       </c>
       <c r="E158">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F158">
-        <v>3.5999999999999999E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="G158">
         <v>1</v>
@@ -16402,10 +18221,10 @@
         <v>0</v>
       </c>
       <c r="K158">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L158">
-        <v>0.2786707944569326</v>
+        <v>0.27361178776426898</v>
       </c>
     </row>
     <row r="159" spans="2:20" x14ac:dyDescent="0.45">
@@ -16416,7 +18235,7 @@
         <v>159</v>
       </c>
       <c r="D159" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E159">
         <v>2011</v>
@@ -16460,7 +18279,19 @@
         <v>0.01</v>
       </c>
       <c r="G160">
-        <v>0.33123000000000002</v>
+        <v>1</v>
+      </c>
+      <c r="H160">
+        <v>1836</v>
+      </c>
+      <c r="I160">
+        <v>46.800000000000004</v>
+      </c>
+      <c r="J160">
+        <v>2.16</v>
+      </c>
+      <c r="K160">
+        <v>41</v>
       </c>
       <c r="L160">
         <v>0.45075539412394755</v>
@@ -16469,4 +18300,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63AC3CE5-646A-422F-A391-DD1AEDA65802}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>